--- a/product-definitions/spreadsheet/halocarbon-concentration.xlsx
+++ b/product-definitions/spreadsheet/halocarbon-concentration.xlsx
@@ -441,7 +441,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -476,11 +476,6 @@
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -502,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -565,7 +560,7 @@
     <xf borderId="0" fillId="2" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -578,12 +573,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2561,7 +2553,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
         <v>19</v>
@@ -2593,7 +2585,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="7"/>
       <c r="B22" s="7" t="s">
         <v>20</v>
@@ -2625,7 +2617,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
       <c r="B23" s="7" t="s">
         <v>22</v>
@@ -2657,7 +2649,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="7"/>
       <c r="B24" s="7" t="s">
         <v>23</v>
@@ -2689,7 +2681,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="7"/>
       <c r="B25" s="7" t="s">
         <v>25</v>
@@ -2721,7 +2713,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="7"/>
       <c r="B26" s="8" t="s">
         <v>26</v>
@@ -2753,7 +2745,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
         <v>28</v>
@@ -2785,7 +2777,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="7"/>
       <c r="B28" s="15" t="s">
         <v>30</v>
@@ -2817,7 +2809,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2845,7 +2837,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
         <v>35</v>
       </c>
@@ -2875,7 +2867,7 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="7" t="s">
         <v>10</v>
@@ -2907,7 +2899,7 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="7"/>
       <c r="B32" s="7" t="s">
         <v>12</v>
@@ -2939,7 +2931,7 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="8"/>
       <c r="B33" s="8" t="s">
         <v>2</v>
@@ -2971,7 +2963,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
         <v>19</v>
@@ -3003,7 +2995,7 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="7"/>
       <c r="B35" s="7" t="s">
         <v>20</v>
@@ -3035,7 +3027,7 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
         <v>22</v>
@@ -3067,7 +3059,7 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="7"/>
       <c r="B37" s="7" t="s">
         <v>23</v>
@@ -3099,7 +3091,7 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="7"/>
       <c r="B38" s="7" t="s">
         <v>25</v>
@@ -3131,7 +3123,7 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="7"/>
       <c r="B39" s="8" t="s">
         <v>26</v>
@@ -3163,7 +3155,7 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7" t="s">
         <v>28</v>
@@ -3195,7 +3187,7 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="7"/>
       <c r="B41" s="15" t="s">
         <v>30</v>
@@ -3227,7 +3219,7 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -3255,7 +3247,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="6" t="s">
         <v>38</v>
       </c>
@@ -3285,7 +3277,7 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="7"/>
       <c r="B44" s="7" t="s">
         <v>10</v>
@@ -3317,7 +3309,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="7"/>
       <c r="B45" s="7" t="s">
         <v>12</v>
@@ -3349,7 +3341,7 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="8"/>
       <c r="B46" s="8" t="s">
         <v>2</v>
@@ -3381,7 +3373,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="7"/>
       <c r="B47" s="7" t="s">
         <v>19</v>
@@ -3413,7 +3405,7 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="7"/>
       <c r="B48" s="7" t="s">
         <v>20</v>
@@ -3445,7 +3437,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="7"/>
       <c r="B49" s="7" t="s">
         <v>22</v>
@@ -3477,7 +3469,7 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7" t="s">
         <v>23</v>
@@ -3509,7 +3501,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="7"/>
       <c r="B51" s="7" t="s">
         <v>25</v>
@@ -3541,7 +3533,7 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="7"/>
       <c r="B52" s="8" t="s">
         <v>26</v>
@@ -3573,7 +3565,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="7"/>
       <c r="B53" s="7" t="s">
         <v>28</v>
@@ -3605,7 +3597,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="7"/>
       <c r="B54" s="15" t="s">
         <v>30</v>
@@ -3637,7 +3629,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="20"/>
       <c r="B55" s="2"/>
       <c r="D55" s="2"/>
@@ -3664,7 +3656,7 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="6" t="s">
         <v>41</v>
       </c>
@@ -3694,7 +3686,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="7"/>
       <c r="B57" s="7" t="s">
         <v>10</v>
@@ -3726,7 +3718,7 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="7"/>
       <c r="B58" s="7" t="s">
         <v>12</v>
@@ -3758,7 +3750,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="8"/>
       <c r="B59" s="8" t="s">
         <v>2</v>
@@ -3792,7 +3784,7 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="8" t="s">
         <v>16</v>
@@ -3826,7 +3818,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="7"/>
       <c r="B61" s="7" t="s">
         <v>19</v>
@@ -3858,7 +3850,7 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="7"/>
       <c r="B62" s="7" t="s">
         <v>20</v>
@@ -3890,7 +3882,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="7"/>
       <c r="B63" s="7" t="s">
         <v>22</v>
@@ -3922,7 +3914,7 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="7"/>
       <c r="B64" s="7" t="s">
         <v>23</v>
@@ -3954,7 +3946,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="7"/>
       <c r="B65" s="7" t="s">
         <v>25</v>
@@ -3986,7 +3978,7 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="7"/>
       <c r="B66" s="8" t="s">
         <v>26</v>
@@ -4018,7 +4010,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="7"/>
       <c r="B67" s="7" t="s">
         <v>28</v>
@@ -4050,7 +4042,7 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="7"/>
       <c r="B68" s="15" t="s">
         <v>30</v>
@@ -4082,7 +4074,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="10"/>
@@ -4110,7 +4102,7 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="6" t="s">
         <v>44</v>
       </c>
@@ -4140,7 +4132,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="7"/>
       <c r="B71" s="7" t="s">
         <v>10</v>
@@ -4172,7 +4164,7 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="7"/>
       <c r="B72" s="7" t="s">
         <v>12</v>
@@ -4204,7 +4196,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="8"/>
       <c r="B73" s="8" t="s">
         <v>2</v>
@@ -4238,7 +4230,7 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="7"/>
       <c r="B74" s="8" t="s">
         <v>16</v>
@@ -4272,7 +4264,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="7"/>
       <c r="B75" s="7" t="s">
         <v>19</v>
@@ -4304,7 +4296,7 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="7"/>
       <c r="B76" s="7" t="s">
         <v>20</v>
@@ -4336,7 +4328,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="7"/>
       <c r="B77" s="7" t="s">
         <v>22</v>
@@ -4368,7 +4360,7 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="7"/>
       <c r="B78" s="7" t="s">
         <v>23</v>
@@ -4400,7 +4392,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="7"/>
       <c r="B79" s="7" t="s">
         <v>25</v>
@@ -4432,7 +4424,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="8" t="s">
         <v>26</v>
@@ -4464,7 +4456,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="7"/>
       <c r="B81" s="7" t="s">
         <v>28</v>
@@ -4496,7 +4488,7 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="7"/>
       <c r="B82" s="15" t="s">
         <v>30</v>
@@ -4528,7 +4520,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -4556,7 +4548,7 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6" t="s">
         <v>46</v>
       </c>
@@ -4586,7 +4578,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="7"/>
       <c r="B85" s="7" t="s">
         <v>10</v>
@@ -4618,7 +4610,7 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="7"/>
       <c r="B86" s="7" t="s">
         <v>12</v>
@@ -4650,7 +4642,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="8"/>
       <c r="B87" s="8" t="s">
         <v>2</v>
@@ -4682,7 +4674,7 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="7"/>
       <c r="B88" s="7" t="s">
         <v>19</v>
@@ -4714,7 +4706,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="7"/>
       <c r="B89" s="7" t="s">
         <v>20</v>
@@ -4746,7 +4738,7 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="7" t="s">
         <v>22</v>
@@ -4778,7 +4770,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="7"/>
       <c r="B91" s="7" t="s">
         <v>23</v>
@@ -4810,7 +4802,7 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="7"/>
       <c r="B92" s="7" t="s">
         <v>25</v>
@@ -4842,7 +4834,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="7"/>
       <c r="B93" s="8" t="s">
         <v>26</v>
@@ -4874,7 +4866,7 @@
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="7"/>
       <c r="B94" s="7" t="s">
         <v>28</v>
@@ -4906,7 +4898,7 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="7"/>
       <c r="B95" s="15" t="s">
         <v>30</v>
@@ -4938,7 +4930,7 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -4966,7 +4958,7 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="6" t="s">
         <v>48</v>
       </c>
@@ -4996,7 +4988,7 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="7"/>
       <c r="B98" s="7" t="s">
         <v>10</v>
@@ -5028,7 +5020,7 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="7"/>
       <c r="B99" s="7" t="s">
         <v>12</v>
@@ -5041,7 +5033,7 @@
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="8"/>
       <c r="B100" s="8" t="s">
         <v>2</v>
@@ -5054,7 +5046,7 @@
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="7"/>
       <c r="B101" s="7" t="s">
         <v>19</v>
@@ -5067,7 +5059,7 @@
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="7"/>
       <c r="B102" s="7" t="s">
         <v>20</v>
@@ -5080,7 +5072,7 @@
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="7"/>
       <c r="B103" s="7" t="s">
         <v>22</v>
@@ -5093,7 +5085,7 @@
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="7"/>
       <c r="B104" s="7" t="s">
         <v>23</v>
@@ -5106,7 +5098,7 @@
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="7"/>
       <c r="B105" s="7" t="s">
         <v>25</v>
@@ -5119,7 +5111,7 @@
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="7"/>
       <c r="B106" s="8" t="s">
         <v>26</v>
@@ -5132,7 +5124,7 @@
       <c r="F106" s="7"/>
       <c r="G106" s="7"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="7"/>
       <c r="B107" s="7" t="s">
         <v>28</v>
@@ -5145,7 +5137,7 @@
       <c r="F107" s="7"/>
       <c r="G107" s="7"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="7"/>
       <c r="B108" s="15" t="s">
         <v>30</v>
@@ -5158,14 +5150,14 @@
       <c r="F108" s="7"/>
       <c r="G108" s="7"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="20"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
       <c r="D109" s="10"/>
       <c r="E109" s="10"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
         <v>50</v>
       </c>
@@ -5176,7 +5168,7 @@
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="7"/>
       <c r="B111" s="7" t="s">
         <v>10</v>
@@ -5189,7 +5181,7 @@
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="7"/>
       <c r="B112" s="7" t="s">
         <v>12</v>
@@ -5202,7 +5194,7 @@
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="8"/>
       <c r="B113" s="8" t="s">
         <v>2</v>
@@ -5236,7 +5228,7 @@
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="7"/>
       <c r="B114" s="8" t="s">
         <v>16</v>
@@ -5270,7 +5262,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="7"/>
       <c r="B115" s="7" t="s">
         <v>19</v>
@@ -5302,7 +5294,7 @@
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="7"/>
       <c r="B116" s="7" t="s">
         <v>20</v>
@@ -5334,7 +5326,7 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="7"/>
       <c r="B117" s="7" t="s">
         <v>22</v>
@@ -5366,7 +5358,7 @@
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="7"/>
       <c r="B118" s="7" t="s">
         <v>23</v>
@@ -5398,7 +5390,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="7"/>
       <c r="B119" s="7" t="s">
         <v>25</v>
@@ -5430,7 +5422,7 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="7"/>
       <c r="B120" s="8" t="s">
         <v>26</v>
@@ -5462,7 +5454,7 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="7"/>
       <c r="B121" s="7" t="s">
         <v>28</v>
@@ -5494,7 +5486,7 @@
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="7"/>
       <c r="B122" s="15" t="s">
         <v>30</v>
@@ -5526,7 +5518,7 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="10"/>
@@ -5554,7 +5546,7 @@
       <c r="Y123" s="2"/>
       <c r="Z123" s="2"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="6" t="s">
         <v>53</v>
       </c>
@@ -5584,7 +5576,7 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="7"/>
       <c r="B125" s="7" t="s">
         <v>10</v>
@@ -5616,7 +5608,7 @@
       <c r="Y125" s="2"/>
       <c r="Z125" s="2"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="7"/>
       <c r="B126" s="7" t="s">
         <v>12</v>
@@ -5648,7 +5640,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="8"/>
       <c r="B127" s="8" t="s">
         <v>2</v>
@@ -5682,7 +5674,7 @@
       <c r="Y127" s="2"/>
       <c r="Z127" s="2"/>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="7"/>
       <c r="B128" s="8" t="s">
         <v>16</v>
@@ -5716,7 +5708,7 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="7"/>
       <c r="B129" s="7" t="s">
         <v>19</v>
@@ -5748,7 +5740,7 @@
       <c r="Y129" s="2"/>
       <c r="Z129" s="2"/>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="7"/>
       <c r="B130" s="7" t="s">
         <v>20</v>
@@ -5780,7 +5772,7 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="7"/>
       <c r="B131" s="7" t="s">
         <v>22</v>
@@ -5812,7 +5804,7 @@
       <c r="Y131" s="2"/>
       <c r="Z131" s="2"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="7"/>
       <c r="B132" s="7" t="s">
         <v>23</v>
@@ -5844,7 +5836,7 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="7"/>
       <c r="B133" s="7" t="s">
         <v>25</v>
@@ -5876,7 +5868,7 @@
       <c r="Y133" s="2"/>
       <c r="Z133" s="2"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="7"/>
       <c r="B134" s="8" t="s">
         <v>26</v>
@@ -5908,7 +5900,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="7"/>
       <c r="B135" s="7" t="s">
         <v>28</v>
@@ -5940,7 +5932,7 @@
       <c r="Y135" s="2"/>
       <c r="Z135" s="2"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="7"/>
       <c r="B136" s="15" t="s">
         <v>30</v>
@@ -5972,7 +5964,7 @@
       <c r="Y136" s="2"/>
       <c r="Z136" s="2"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -6000,7 +5992,7 @@
       <c r="Y137" s="2"/>
       <c r="Z137" s="2"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="6" t="s">
         <v>55</v>
       </c>
@@ -6030,7 +6022,7 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="7"/>
       <c r="B139" s="7" t="s">
         <v>10</v>
@@ -6062,7 +6054,7 @@
       <c r="Y139" s="2"/>
       <c r="Z139" s="2"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="7"/>
       <c r="B140" s="7" t="s">
         <v>12</v>
@@ -6094,7 +6086,7 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="8"/>
       <c r="B141" s="8" t="s">
         <v>2</v>
@@ -6126,7 +6118,7 @@
       <c r="Y141" s="2"/>
       <c r="Z141" s="2"/>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="7"/>
       <c r="B142" s="7" t="s">
         <v>19</v>
@@ -6158,7 +6150,7 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="7"/>
       <c r="B143" s="7" t="s">
         <v>20</v>
@@ -6190,7 +6182,7 @@
       <c r="Y143" s="2"/>
       <c r="Z143" s="2"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="7"/>
       <c r="B144" s="7" t="s">
         <v>22</v>
@@ -6222,7 +6214,7 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="7"/>
       <c r="B145" s="7" t="s">
         <v>23</v>
@@ -6254,7 +6246,7 @@
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="7"/>
       <c r="B146" s="7" t="s">
         <v>25</v>
@@ -6286,7 +6278,7 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="7"/>
       <c r="B147" s="8" t="s">
         <v>26</v>
@@ -6318,7 +6310,7 @@
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="7"/>
       <c r="B148" s="7" t="s">
         <v>28</v>
@@ -6350,7 +6342,7 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="7"/>
       <c r="B149" s="15" t="s">
         <v>30</v>
@@ -6382,7 +6374,7 @@
       <c r="Y149" s="2"/>
       <c r="Z149" s="2"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -6410,7 +6402,7 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="6" t="s">
         <v>57</v>
       </c>
@@ -6440,7 +6432,7 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="7"/>
       <c r="B152" s="7" t="s">
         <v>10</v>
@@ -6472,7 +6464,7 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="7"/>
       <c r="B153" s="7" t="s">
         <v>12</v>
@@ -6504,7 +6496,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="8"/>
       <c r="B154" s="8" t="s">
         <v>2</v>
@@ -6536,7 +6528,7 @@
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="7"/>
       <c r="B155" s="7" t="s">
         <v>19</v>
@@ -6568,7 +6560,7 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="7"/>
       <c r="B156" s="7" t="s">
         <v>20</v>
@@ -6600,7 +6592,7 @@
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="7"/>
       <c r="B157" s="7" t="s">
         <v>22</v>
@@ -6632,7 +6624,7 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="7"/>
       <c r="B158" s="7" t="s">
         <v>23</v>
@@ -6664,7 +6656,7 @@
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="7"/>
       <c r="B159" s="7" t="s">
         <v>25</v>
@@ -6696,7 +6688,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="7"/>
       <c r="B160" s="8" t="s">
         <v>26</v>
@@ -6728,7 +6720,7 @@
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="7"/>
       <c r="B161" s="7" t="s">
         <v>28</v>
@@ -6760,7 +6752,7 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="7"/>
       <c r="B162" s="15" t="s">
         <v>30</v>
@@ -6792,7 +6784,7 @@
       <c r="Y162" s="2"/>
       <c r="Z162" s="2"/>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="25"/>
       <c r="B163" s="2"/>
       <c r="C163" s="26"/>
@@ -6820,7 +6812,7 @@
       <c r="Y163" s="2"/>
       <c r="Z163" s="2"/>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="6" t="s">
         <v>60</v>
       </c>
@@ -6850,7 +6842,7 @@
       <c r="Y164" s="2"/>
       <c r="Z164" s="2"/>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="7"/>
       <c r="B165" s="7" t="s">
         <v>10</v>
@@ -6882,7 +6874,7 @@
       <c r="Y165" s="2"/>
       <c r="Z165" s="2"/>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="7"/>
       <c r="B166" s="7" t="s">
         <v>12</v>
@@ -6914,7 +6906,7 @@
       <c r="Y166" s="2"/>
       <c r="Z166" s="2"/>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="8"/>
       <c r="B167" s="8" t="s">
         <v>2</v>
@@ -6948,7 +6940,7 @@
       <c r="Y167" s="2"/>
       <c r="Z167" s="2"/>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="7"/>
       <c r="B168" s="8" t="s">
         <v>16</v>
@@ -6982,7 +6974,7 @@
       <c r="Y168" s="2"/>
       <c r="Z168" s="2"/>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="7"/>
       <c r="B169" s="7" t="s">
         <v>19</v>
@@ -7014,7 +7006,7 @@
       <c r="Y169" s="2"/>
       <c r="Z169" s="2"/>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="7"/>
       <c r="B170" s="7" t="s">
         <v>20</v>
@@ -7046,7 +7038,7 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="7"/>
       <c r="B171" s="7" t="s">
         <v>22</v>
@@ -7078,7 +7070,7 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="7"/>
       <c r="B172" s="7" t="s">
         <v>23</v>
@@ -7110,7 +7102,7 @@
       <c r="Y172" s="2"/>
       <c r="Z172" s="2"/>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="7"/>
       <c r="B173" s="7" t="s">
         <v>25</v>
@@ -7142,7 +7134,7 @@
       <c r="Y173" s="2"/>
       <c r="Z173" s="2"/>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="7"/>
       <c r="B174" s="8" t="s">
         <v>26</v>
@@ -7174,7 +7166,7 @@
       <c r="Y174" s="2"/>
       <c r="Z174" s="2"/>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="7"/>
       <c r="B175" s="7" t="s">
         <v>28</v>
@@ -7206,7 +7198,7 @@
       <c r="Y175" s="2"/>
       <c r="Z175" s="2"/>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="7"/>
       <c r="B176" s="15" t="s">
         <v>30</v>
@@ -7238,7 +7230,7 @@
       <c r="Y176" s="2"/>
       <c r="Z176" s="2"/>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
       <c r="C177" s="10"/>
@@ -7266,7 +7258,7 @@
       <c r="Y177" s="2"/>
       <c r="Z177" s="2"/>
     </row>
-    <row r="178">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="6" t="s">
         <v>63</v>
       </c>
@@ -7296,7 +7288,7 @@
       <c r="Y178" s="2"/>
       <c r="Z178" s="2"/>
     </row>
-    <row r="179">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="7"/>
       <c r="B179" s="7" t="s">
         <v>10</v>
@@ -7328,7 +7320,7 @@
       <c r="Y179" s="2"/>
       <c r="Z179" s="2"/>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="7"/>
       <c r="B180" s="7" t="s">
         <v>12</v>
@@ -7360,7 +7352,7 @@
       <c r="Y180" s="2"/>
       <c r="Z180" s="2"/>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="8"/>
       <c r="B181" s="8" t="s">
         <v>2</v>
@@ -7375,7 +7367,7 @@
       </c>
       <c r="G181" s="7"/>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="7"/>
       <c r="B182" s="8" t="s">
         <v>16</v>
@@ -7390,7 +7382,7 @@
       </c>
       <c r="G182" s="10"/>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="7"/>
       <c r="B183" s="7" t="s">
         <v>19</v>
@@ -7403,7 +7395,7 @@
       <c r="F183" s="7"/>
       <c r="G183" s="7"/>
     </row>
-    <row r="184">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="7"/>
       <c r="B184" s="7" t="s">
         <v>20</v>
@@ -7416,7 +7408,7 @@
       <c r="F184" s="7"/>
       <c r="G184" s="7"/>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="7"/>
       <c r="B185" s="7" t="s">
         <v>22</v>
@@ -7429,7 +7421,7 @@
       <c r="F185" s="7"/>
       <c r="G185" s="7"/>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="7"/>
       <c r="B186" s="7" t="s">
         <v>23</v>
@@ -7442,7 +7434,7 @@
       <c r="F186" s="7"/>
       <c r="G186" s="7"/>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="7"/>
       <c r="B187" s="7" t="s">
         <v>25</v>
@@ -7455,7 +7447,7 @@
       <c r="F187" s="7"/>
       <c r="G187" s="7"/>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="7"/>
       <c r="B188" s="8" t="s">
         <v>26</v>
@@ -7468,7 +7460,7 @@
       <c r="F188" s="7"/>
       <c r="G188" s="7"/>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="7"/>
       <c r="B189" s="7" t="s">
         <v>28</v>
@@ -7481,7 +7473,7 @@
       <c r="F189" s="7"/>
       <c r="G189" s="7"/>
     </row>
-    <row r="190">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="7"/>
       <c r="B190" s="15" t="s">
         <v>30</v>
@@ -7513,7 +7505,7 @@
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
     </row>
-    <row r="191">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="7"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
@@ -7541,7 +7533,7 @@
       <c r="Y191" s="2"/>
       <c r="Z191" s="2"/>
     </row>
-    <row r="192">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="6" t="s">
         <v>65</v>
       </c>
@@ -7571,7 +7563,7 @@
       <c r="Y192" s="2"/>
       <c r="Z192" s="2"/>
     </row>
-    <row r="193">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="7"/>
       <c r="B193" s="7" t="s">
         <v>10</v>
@@ -7603,7 +7595,7 @@
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
     </row>
-    <row r="194">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="7"/>
       <c r="B194" s="7" t="s">
         <v>12</v>
@@ -7635,7 +7627,7 @@
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
     </row>
-    <row r="195">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="8"/>
       <c r="B195" s="8" t="s">
         <v>2</v>
@@ -7667,7 +7659,7 @@
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
     </row>
-    <row r="196">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="7"/>
       <c r="B196" s="7" t="s">
         <v>19</v>
@@ -7699,7 +7691,7 @@
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
     </row>
-    <row r="197">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="7"/>
       <c r="B197" s="7" t="s">
         <v>20</v>
@@ -7731,7 +7723,7 @@
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
     </row>
-    <row r="198">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="7"/>
       <c r="B198" s="7" t="s">
         <v>22</v>
@@ -7744,7 +7736,7 @@
       <c r="F198" s="7"/>
       <c r="G198" s="7"/>
     </row>
-    <row r="199">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="7"/>
       <c r="B199" s="7" t="s">
         <v>23</v>
@@ -7757,7 +7749,7 @@
       <c r="F199" s="7"/>
       <c r="G199" s="7"/>
     </row>
-    <row r="200">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="7"/>
       <c r="B200" s="7" t="s">
         <v>25</v>
@@ -7770,7 +7762,7 @@
       <c r="F200" s="7"/>
       <c r="G200" s="7"/>
     </row>
-    <row r="201">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="7"/>
       <c r="B201" s="8" t="s">
         <v>26</v>
@@ -7783,7 +7775,7 @@
       <c r="F201" s="7"/>
       <c r="G201" s="7"/>
     </row>
-    <row r="202">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="7"/>
       <c r="B202" s="7" t="s">
         <v>28</v>
@@ -7796,7 +7788,7 @@
       <c r="F202" s="7"/>
       <c r="G202" s="7"/>
     </row>
-    <row r="203">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="7"/>
       <c r="B203" s="15" t="s">
         <v>30</v>
@@ -7809,7 +7801,7 @@
       <c r="F203" s="7"/>
       <c r="G203" s="7"/>
     </row>
-    <row r="204">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
@@ -7818,7 +7810,7 @@
       <c r="F204" s="7"/>
       <c r="G204" s="7"/>
     </row>
-    <row r="205">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="6" t="s">
         <v>67</v>
       </c>
@@ -7829,7 +7821,7 @@
       <c r="F205" s="7"/>
       <c r="G205" s="7"/>
     </row>
-    <row r="206">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="7"/>
       <c r="B206" s="7" t="s">
         <v>10</v>
@@ -7842,7 +7834,7 @@
       <c r="F206" s="7"/>
       <c r="G206" s="7"/>
     </row>
-    <row r="207">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="7"/>
       <c r="B207" s="7" t="s">
         <v>12</v>
@@ -7855,7 +7847,7 @@
       <c r="F207" s="7"/>
       <c r="G207" s="7"/>
     </row>
-    <row r="208">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="8"/>
       <c r="B208" s="8" t="s">
         <v>2</v>
@@ -7868,7 +7860,7 @@
       <c r="F208" s="7"/>
       <c r="G208" s="7"/>
     </row>
-    <row r="209">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="7"/>
       <c r="B209" s="7" t="s">
         <v>19</v>
@@ -7881,7 +7873,7 @@
       <c r="F209" s="7"/>
       <c r="G209" s="7"/>
     </row>
-    <row r="210">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="7"/>
       <c r="B210" s="7" t="s">
         <v>20</v>
@@ -7894,7 +7886,7 @@
       <c r="F210" s="7"/>
       <c r="G210" s="7"/>
     </row>
-    <row r="211">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="7"/>
       <c r="B211" s="7" t="s">
         <v>22</v>
@@ -7907,7 +7899,7 @@
       <c r="F211" s="7"/>
       <c r="G211" s="7"/>
     </row>
-    <row r="212">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="7"/>
       <c r="B212" s="7" t="s">
         <v>23</v>
@@ -7920,7 +7912,7 @@
       <c r="F212" s="7"/>
       <c r="G212" s="7"/>
     </row>
-    <row r="213">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="7"/>
       <c r="B213" s="7" t="s">
         <v>25</v>
@@ -7933,7 +7925,7 @@
       <c r="F213" s="7"/>
       <c r="G213" s="7"/>
     </row>
-    <row r="214">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="7"/>
       <c r="B214" s="8" t="s">
         <v>26</v>
@@ -7946,7 +7938,7 @@
       <c r="F214" s="7"/>
       <c r="G214" s="7"/>
     </row>
-    <row r="215">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="7"/>
       <c r="B215" s="7" t="s">
         <v>28</v>
@@ -7959,7 +7951,7 @@
       <c r="F215" s="7"/>
       <c r="G215" s="7"/>
     </row>
-    <row r="216">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="7"/>
       <c r="B216" s="15" t="s">
         <v>30</v>
@@ -7972,11 +7964,11 @@
       <c r="F216" s="7"/>
       <c r="G216" s="7"/>
     </row>
-    <row r="217">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="28"/>
       <c r="C217" s="22"/>
     </row>
-    <row r="218">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="6" t="s">
         <v>69</v>
       </c>
@@ -7987,7 +7979,7 @@
       <c r="F218" s="7"/>
       <c r="G218" s="7"/>
     </row>
-    <row r="219">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="7"/>
       <c r="B219" s="7" t="s">
         <v>10</v>
@@ -8000,7 +7992,7 @@
       <c r="F219" s="7"/>
       <c r="G219" s="7"/>
     </row>
-    <row r="220">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="7"/>
       <c r="B220" s="7" t="s">
         <v>12</v>
@@ -8013,7 +8005,7 @@
       <c r="F220" s="7"/>
       <c r="G220" s="7"/>
     </row>
-    <row r="221">
+    <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="8"/>
       <c r="B221" s="8" t="s">
         <v>2</v>
@@ -8028,7 +8020,7 @@
       </c>
       <c r="G221" s="10"/>
     </row>
-    <row r="222">
+    <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="7"/>
       <c r="B222" s="8" t="s">
         <v>16</v>
@@ -8043,7 +8035,7 @@
       </c>
       <c r="G222" s="7"/>
     </row>
-    <row r="223">
+    <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="7"/>
       <c r="B223" s="7" t="s">
         <v>19</v>
@@ -8056,7 +8048,7 @@
       <c r="F223" s="7"/>
       <c r="G223" s="7"/>
     </row>
-    <row r="224">
+    <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="7"/>
       <c r="B224" s="7" t="s">
         <v>20</v>
@@ -8069,7 +8061,7 @@
       <c r="F224" s="7"/>
       <c r="G224" s="7"/>
     </row>
-    <row r="225">
+    <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="7"/>
       <c r="B225" s="7" t="s">
         <v>22</v>
@@ -8082,7 +8074,7 @@
       <c r="F225" s="7"/>
       <c r="G225" s="7"/>
     </row>
-    <row r="226">
+    <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="7"/>
       <c r="B226" s="7" t="s">
         <v>23</v>
@@ -8095,7 +8087,7 @@
       <c r="F226" s="7"/>
       <c r="G226" s="7"/>
     </row>
-    <row r="227">
+    <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="7"/>
       <c r="B227" s="7" t="s">
         <v>25</v>
@@ -8108,7 +8100,7 @@
       <c r="F227" s="7"/>
       <c r="G227" s="7"/>
     </row>
-    <row r="228">
+    <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="7"/>
       <c r="B228" s="8" t="s">
         <v>26</v>
@@ -8121,7 +8113,7 @@
       <c r="F228" s="7"/>
       <c r="G228" s="7"/>
     </row>
-    <row r="229">
+    <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="7"/>
       <c r="B229" s="7" t="s">
         <v>28</v>
@@ -8134,7 +8126,7 @@
       <c r="F229" s="7"/>
       <c r="G229" s="7"/>
     </row>
-    <row r="230">
+    <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="7"/>
       <c r="B230" s="15" t="s">
         <v>30</v>
@@ -8147,7 +8139,7 @@
       <c r="F230" s="7"/>
       <c r="G230" s="7"/>
     </row>
-    <row r="231">
+    <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
       <c r="C231" s="10"/>
@@ -8156,7 +8148,7 @@
       <c r="F231" s="7"/>
       <c r="G231" s="7"/>
     </row>
-    <row r="232">
+    <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="6" t="s">
         <v>72</v>
       </c>
@@ -8167,7 +8159,7 @@
       <c r="F232" s="7"/>
       <c r="G232" s="7"/>
     </row>
-    <row r="233">
+    <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="7"/>
       <c r="B233" s="7" t="s">
         <v>10</v>
@@ -8180,7 +8172,7 @@
       <c r="F233" s="7"/>
       <c r="G233" s="7"/>
     </row>
-    <row r="234">
+    <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="7"/>
       <c r="B234" s="7" t="s">
         <v>12</v>
@@ -8193,7 +8185,7 @@
       <c r="F234" s="7"/>
       <c r="G234" s="7"/>
     </row>
-    <row r="235">
+    <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="8"/>
       <c r="B235" s="8" t="s">
         <v>2</v>
@@ -8208,7 +8200,7 @@
       </c>
       <c r="G235" s="7"/>
     </row>
-    <row r="236">
+    <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="7"/>
       <c r="B236" s="8" t="s">
         <v>16</v>
@@ -8223,7 +8215,7 @@
       </c>
       <c r="G236" s="10"/>
     </row>
-    <row r="237">
+    <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="7"/>
       <c r="B237" s="7" t="s">
         <v>19</v>
@@ -8236,7 +8228,7 @@
       <c r="F237" s="7"/>
       <c r="G237" s="7"/>
     </row>
-    <row r="238">
+    <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="7"/>
       <c r="B238" s="7" t="s">
         <v>20</v>
@@ -8249,7 +8241,7 @@
       <c r="F238" s="7"/>
       <c r="G238" s="7"/>
     </row>
-    <row r="239">
+    <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="7"/>
       <c r="B239" s="7" t="s">
         <v>22</v>
@@ -8262,7 +8254,7 @@
       <c r="F239" s="7"/>
       <c r="G239" s="7"/>
     </row>
-    <row r="240">
+    <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="7"/>
       <c r="B240" s="7" t="s">
         <v>23</v>
@@ -8275,7 +8267,7 @@
       <c r="F240" s="7"/>
       <c r="G240" s="7"/>
     </row>
-    <row r="241">
+    <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="7"/>
       <c r="B241" s="7" t="s">
         <v>25</v>
@@ -8288,7 +8280,7 @@
       <c r="F241" s="7"/>
       <c r="G241" s="7"/>
     </row>
-    <row r="242">
+    <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="7"/>
       <c r="B242" s="8" t="s">
         <v>26</v>
@@ -8301,7 +8293,7 @@
       <c r="F242" s="7"/>
       <c r="G242" s="7"/>
     </row>
-    <row r="243">
+    <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="7"/>
       <c r="B243" s="7" t="s">
         <v>28</v>
@@ -8314,7 +8306,7 @@
       <c r="F243" s="7"/>
       <c r="G243" s="7"/>
     </row>
-    <row r="244">
+    <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="7"/>
       <c r="B244" s="15" t="s">
         <v>30</v>
@@ -8327,7 +8319,7 @@
       <c r="F244" s="7"/>
       <c r="G244" s="7"/>
     </row>
-    <row r="245">
+    <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="7"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
@@ -8336,7 +8328,7 @@
       <c r="F245" s="7"/>
       <c r="G245" s="7"/>
     </row>
-    <row r="246">
+    <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="6" t="s">
         <v>74</v>
       </c>
@@ -8347,7 +8339,7 @@
       <c r="F246" s="7"/>
       <c r="G246" s="7"/>
     </row>
-    <row r="247">
+    <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="7"/>
       <c r="B247" s="7" t="s">
         <v>10</v>
@@ -8360,7 +8352,7 @@
       <c r="F247" s="7"/>
       <c r="G247" s="7"/>
     </row>
-    <row r="248">
+    <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="7"/>
       <c r="B248" s="7" t="s">
         <v>12</v>
@@ -8373,7 +8365,7 @@
       <c r="F248" s="7"/>
       <c r="G248" s="7"/>
     </row>
-    <row r="249">
+    <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="8"/>
       <c r="B249" s="8" t="s">
         <v>2</v>
@@ -8386,7 +8378,7 @@
       <c r="F249" s="10"/>
       <c r="G249" s="7"/>
     </row>
-    <row r="250">
+    <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="7"/>
       <c r="B250" s="7" t="s">
         <v>19</v>
@@ -8399,7 +8391,7 @@
       <c r="F250" s="7"/>
       <c r="G250" s="7"/>
     </row>
-    <row r="251">
+    <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="7"/>
       <c r="B251" s="7" t="s">
         <v>20</v>
@@ -8412,7 +8404,7 @@
       <c r="F251" s="7"/>
       <c r="G251" s="7"/>
     </row>
-    <row r="252">
+    <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="7"/>
       <c r="B252" s="7" t="s">
         <v>22</v>
@@ -8425,7 +8417,7 @@
       <c r="F252" s="7"/>
       <c r="G252" s="7"/>
     </row>
-    <row r="253">
+    <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="7"/>
       <c r="B253" s="7" t="s">
         <v>23</v>
@@ -8438,7 +8430,7 @@
       <c r="F253" s="7"/>
       <c r="G253" s="7"/>
     </row>
-    <row r="254">
+    <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="7"/>
       <c r="B254" s="7" t="s">
         <v>25</v>
@@ -8451,7 +8443,7 @@
       <c r="F254" s="7"/>
       <c r="G254" s="7"/>
     </row>
-    <row r="255">
+    <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="7"/>
       <c r="B255" s="8" t="s">
         <v>26</v>
@@ -8464,7 +8456,7 @@
       <c r="F255" s="7"/>
       <c r="G255" s="7"/>
     </row>
-    <row r="256">
+    <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="7"/>
       <c r="B256" s="7" t="s">
         <v>28</v>
@@ -8477,7 +8469,7 @@
       <c r="F256" s="7"/>
       <c r="G256" s="7"/>
     </row>
-    <row r="257">
+    <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="7"/>
       <c r="B257" s="15" t="s">
         <v>30</v>
@@ -8490,7 +8482,7 @@
       <c r="F257" s="7"/>
       <c r="G257" s="7"/>
     </row>
-    <row r="258">
+    <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7"/>
@@ -8499,7 +8491,7 @@
       <c r="F258" s="7"/>
       <c r="G258" s="7"/>
     </row>
-    <row r="259">
+    <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="6" t="s">
         <v>76</v>
       </c>
@@ -8510,7 +8502,7 @@
       <c r="F259" s="7"/>
       <c r="G259" s="7"/>
     </row>
-    <row r="260">
+    <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="7"/>
       <c r="B260" s="7" t="s">
         <v>10</v>
@@ -8523,7 +8515,7 @@
       <c r="F260" s="7"/>
       <c r="G260" s="7"/>
     </row>
-    <row r="261">
+    <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="7"/>
       <c r="B261" s="7" t="s">
         <v>12</v>
@@ -8536,7 +8528,7 @@
       <c r="F261" s="7"/>
       <c r="G261" s="7"/>
     </row>
-    <row r="262">
+    <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="8"/>
       <c r="B262" s="8" t="s">
         <v>2</v>
@@ -8549,7 +8541,7 @@
       <c r="F262" s="7"/>
       <c r="G262" s="7"/>
     </row>
-    <row r="263">
+    <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="7"/>
       <c r="B263" s="7" t="s">
         <v>19</v>
@@ -8562,7 +8554,7 @@
       <c r="F263" s="7"/>
       <c r="G263" s="7"/>
     </row>
-    <row r="264">
+    <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="7"/>
       <c r="B264" s="7" t="s">
         <v>20</v>
@@ -8575,7 +8567,7 @@
       <c r="F264" s="7"/>
       <c r="G264" s="7"/>
     </row>
-    <row r="265">
+    <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="7"/>
       <c r="B265" s="7" t="s">
         <v>22</v>
@@ -8588,7 +8580,7 @@
       <c r="F265" s="7"/>
       <c r="G265" s="7"/>
     </row>
-    <row r="266">
+    <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="7"/>
       <c r="B266" s="7" t="s">
         <v>23</v>
@@ -8601,7 +8593,7 @@
       <c r="F266" s="7"/>
       <c r="G266" s="7"/>
     </row>
-    <row r="267">
+    <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="7"/>
       <c r="B267" s="7" t="s">
         <v>25</v>
@@ -8614,7 +8606,7 @@
       <c r="F267" s="7"/>
       <c r="G267" s="7"/>
     </row>
-    <row r="268">
+    <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="7"/>
       <c r="B268" s="8" t="s">
         <v>26</v>
@@ -8627,7 +8619,7 @@
       <c r="F268" s="7"/>
       <c r="G268" s="7"/>
     </row>
-    <row r="269">
+    <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="7"/>
       <c r="B269" s="7" t="s">
         <v>28</v>
@@ -8640,7 +8632,7 @@
       <c r="F269" s="7"/>
       <c r="G269" s="7"/>
     </row>
-    <row r="270">
+    <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="7"/>
       <c r="B270" s="15" t="s">
         <v>30</v>
@@ -8653,11 +8645,11 @@
       <c r="F270" s="7"/>
       <c r="G270" s="7"/>
     </row>
-    <row r="271">
+    <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="28"/>
       <c r="C271" s="22"/>
     </row>
-    <row r="272">
+    <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="6" t="s">
         <v>78</v>
       </c>
@@ -8668,7 +8660,7 @@
       <c r="F272" s="7"/>
       <c r="G272" s="7"/>
     </row>
-    <row r="273">
+    <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="7"/>
       <c r="B273" s="7" t="s">
         <v>10</v>
@@ -8681,7 +8673,7 @@
       <c r="F273" s="7"/>
       <c r="G273" s="7"/>
     </row>
-    <row r="274">
+    <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="7"/>
       <c r="B274" s="7" t="s">
         <v>12</v>
@@ -8694,7 +8686,7 @@
       <c r="F274" s="7"/>
       <c r="G274" s="7"/>
     </row>
-    <row r="275">
+    <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="8"/>
       <c r="B275" s="8" t="s">
         <v>2</v>
@@ -8709,7 +8701,7 @@
       </c>
       <c r="G275" s="10"/>
     </row>
-    <row r="276">
+    <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="7"/>
       <c r="B276" s="8" t="s">
         <v>16</v>
@@ -8724,7 +8716,7 @@
       </c>
       <c r="G276" s="7"/>
     </row>
-    <row r="277">
+    <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="7"/>
       <c r="B277" s="7" t="s">
         <v>19</v>
@@ -8737,7 +8729,7 @@
       <c r="F277" s="7"/>
       <c r="G277" s="7"/>
     </row>
-    <row r="278">
+    <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="7"/>
       <c r="B278" s="7" t="s">
         <v>20</v>
@@ -8750,7 +8742,7 @@
       <c r="F278" s="7"/>
       <c r="G278" s="7"/>
     </row>
-    <row r="279">
+    <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="7"/>
       <c r="B279" s="7" t="s">
         <v>22</v>
@@ -8763,7 +8755,7 @@
       <c r="F279" s="7"/>
       <c r="G279" s="7"/>
     </row>
-    <row r="280">
+    <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="7"/>
       <c r="B280" s="7" t="s">
         <v>23</v>
@@ -8776,7 +8768,7 @@
       <c r="F280" s="7"/>
       <c r="G280" s="7"/>
     </row>
-    <row r="281">
+    <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="7"/>
       <c r="B281" s="7" t="s">
         <v>25</v>
@@ -8789,7 +8781,7 @@
       <c r="F281" s="7"/>
       <c r="G281" s="7"/>
     </row>
-    <row r="282">
+    <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="7"/>
       <c r="B282" s="8" t="s">
         <v>26</v>
@@ -8802,7 +8794,7 @@
       <c r="F282" s="7"/>
       <c r="G282" s="7"/>
     </row>
-    <row r="283">
+    <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="7"/>
       <c r="B283" s="7" t="s">
         <v>28</v>
@@ -8815,7 +8807,7 @@
       <c r="F283" s="7"/>
       <c r="G283" s="7"/>
     </row>
-    <row r="284">
+    <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="7"/>
       <c r="B284" s="15" t="s">
         <v>30</v>
@@ -8828,7 +8820,7 @@
       <c r="F284" s="7"/>
       <c r="G284" s="7"/>
     </row>
-    <row r="285">
+    <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="7"/>
       <c r="B285" s="7"/>
       <c r="C285" s="10"/>
@@ -8837,7 +8829,7 @@
       <c r="F285" s="7"/>
       <c r="G285" s="7"/>
     </row>
-    <row r="286">
+    <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="6" t="s">
         <v>81</v>
       </c>
@@ -8848,7 +8840,7 @@
       <c r="F286" s="7"/>
       <c r="G286" s="7"/>
     </row>
-    <row r="287">
+    <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="7"/>
       <c r="B287" s="7" t="s">
         <v>10</v>
@@ -8861,7 +8853,7 @@
       <c r="F287" s="7"/>
       <c r="G287" s="7"/>
     </row>
-    <row r="288">
+    <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="7"/>
       <c r="B288" s="7" t="s">
         <v>12</v>
@@ -8874,7 +8866,7 @@
       <c r="F288" s="7"/>
       <c r="G288" s="7"/>
     </row>
-    <row r="289">
+    <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="8"/>
       <c r="B289" s="8" t="s">
         <v>2</v>
@@ -8889,7 +8881,7 @@
       </c>
       <c r="G289" s="7"/>
     </row>
-    <row r="290">
+    <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="7"/>
       <c r="B290" s="8" t="s">
         <v>16</v>
@@ -8904,7 +8896,7 @@
       </c>
       <c r="G290" s="10"/>
     </row>
-    <row r="291">
+    <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="7"/>
       <c r="B291" s="7" t="s">
         <v>19</v>
@@ -8917,7 +8909,7 @@
       <c r="F291" s="7"/>
       <c r="G291" s="7"/>
     </row>
-    <row r="292">
+    <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="7"/>
       <c r="B292" s="7" t="s">
         <v>20</v>
@@ -8930,7 +8922,7 @@
       <c r="F292" s="7"/>
       <c r="G292" s="7"/>
     </row>
-    <row r="293">
+    <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="7"/>
       <c r="B293" s="7" t="s">
         <v>22</v>
@@ -8943,7 +8935,7 @@
       <c r="F293" s="7"/>
       <c r="G293" s="7"/>
     </row>
-    <row r="294">
+    <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="7"/>
       <c r="B294" s="7" t="s">
         <v>23</v>
@@ -8956,7 +8948,7 @@
       <c r="F294" s="7"/>
       <c r="G294" s="7"/>
     </row>
-    <row r="295">
+    <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="7"/>
       <c r="B295" s="7" t="s">
         <v>25</v>
@@ -8969,7 +8961,7 @@
       <c r="F295" s="7"/>
       <c r="G295" s="7"/>
     </row>
-    <row r="296">
+    <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="7"/>
       <c r="B296" s="8" t="s">
         <v>26</v>
@@ -8982,7 +8974,7 @@
       <c r="F296" s="7"/>
       <c r="G296" s="7"/>
     </row>
-    <row r="297">
+    <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="7"/>
       <c r="B297" s="7" t="s">
         <v>28</v>
@@ -8995,7 +8987,7 @@
       <c r="F297" s="7"/>
       <c r="G297" s="7"/>
     </row>
-    <row r="298">
+    <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="7"/>
       <c r="B298" s="15" t="s">
         <v>30</v>
@@ -9008,7 +9000,7 @@
       <c r="F298" s="7"/>
       <c r="G298" s="7"/>
     </row>
-    <row r="299">
+    <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="7"/>
       <c r="B299" s="7"/>
       <c r="C299" s="7"/>
@@ -9017,7 +9009,7 @@
       <c r="F299" s="7"/>
       <c r="G299" s="7"/>
     </row>
-    <row r="300">
+    <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="6" t="s">
         <v>83</v>
       </c>
@@ -9028,7 +9020,7 @@
       <c r="F300" s="7"/>
       <c r="G300" s="7"/>
     </row>
-    <row r="301">
+    <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="7"/>
       <c r="B301" s="7" t="s">
         <v>10</v>
@@ -9041,7 +9033,7 @@
       <c r="F301" s="7"/>
       <c r="G301" s="7"/>
     </row>
-    <row r="302">
+    <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="7"/>
       <c r="B302" s="7" t="s">
         <v>12</v>
@@ -9054,7 +9046,7 @@
       <c r="F302" s="7"/>
       <c r="G302" s="7"/>
     </row>
-    <row r="303">
+    <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="8"/>
       <c r="B303" s="8" t="s">
         <v>2</v>
@@ -9067,7 +9059,7 @@
       <c r="F303" s="10"/>
       <c r="G303" s="7"/>
     </row>
-    <row r="304">
+    <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="7"/>
       <c r="B304" s="7" t="s">
         <v>19</v>
@@ -9080,7 +9072,7 @@
       <c r="F304" s="7"/>
       <c r="G304" s="7"/>
     </row>
-    <row r="305">
+    <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="7"/>
       <c r="B305" s="7" t="s">
         <v>20</v>
@@ -9093,7 +9085,7 @@
       <c r="F305" s="7"/>
       <c r="G305" s="7"/>
     </row>
-    <row r="306">
+    <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="7"/>
       <c r="B306" s="7" t="s">
         <v>22</v>
@@ -9106,7 +9098,7 @@
       <c r="F306" s="7"/>
       <c r="G306" s="7"/>
     </row>
-    <row r="307">
+    <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="7"/>
       <c r="B307" s="7" t="s">
         <v>23</v>
@@ -9119,7 +9111,7 @@
       <c r="F307" s="7"/>
       <c r="G307" s="7"/>
     </row>
-    <row r="308">
+    <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="7"/>
       <c r="B308" s="7" t="s">
         <v>25</v>
@@ -9132,7 +9124,7 @@
       <c r="F308" s="7"/>
       <c r="G308" s="7"/>
     </row>
-    <row r="309">
+    <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="7"/>
       <c r="B309" s="8" t="s">
         <v>26</v>
@@ -9145,7 +9137,7 @@
       <c r="F309" s="7"/>
       <c r="G309" s="7"/>
     </row>
-    <row r="310">
+    <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="7"/>
       <c r="B310" s="7" t="s">
         <v>28</v>
@@ -9158,7 +9150,7 @@
       <c r="F310" s="7"/>
       <c r="G310" s="7"/>
     </row>
-    <row r="311">
+    <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="7"/>
       <c r="B311" s="15" t="s">
         <v>30</v>
@@ -9171,7 +9163,7 @@
       <c r="F311" s="7"/>
       <c r="G311" s="7"/>
     </row>
-    <row r="312">
+    <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="7"/>
       <c r="B312" s="7"/>
       <c r="C312" s="7"/>
@@ -9180,7 +9172,7 @@
       <c r="F312" s="7"/>
       <c r="G312" s="7"/>
     </row>
-    <row r="313">
+    <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="6" t="s">
         <v>85</v>
       </c>
@@ -9191,7 +9183,7 @@
       <c r="F313" s="7"/>
       <c r="G313" s="7"/>
     </row>
-    <row r="314">
+    <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="7"/>
       <c r="B314" s="7" t="s">
         <v>10</v>
@@ -9204,7 +9196,7 @@
       <c r="F314" s="7"/>
       <c r="G314" s="7"/>
     </row>
-    <row r="315">
+    <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="7"/>
       <c r="B315" s="7" t="s">
         <v>12</v>
@@ -9217,7 +9209,7 @@
       <c r="F315" s="7"/>
       <c r="G315" s="7"/>
     </row>
-    <row r="316">
+    <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="8"/>
       <c r="B316" s="8" t="s">
         <v>2</v>
@@ -9230,7 +9222,7 @@
       <c r="F316" s="7"/>
       <c r="G316" s="7"/>
     </row>
-    <row r="317">
+    <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="7"/>
       <c r="B317" s="7" t="s">
         <v>19</v>
@@ -9243,7 +9235,7 @@
       <c r="F317" s="7"/>
       <c r="G317" s="7"/>
     </row>
-    <row r="318">
+    <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="7"/>
       <c r="B318" s="7" t="s">
         <v>20</v>
@@ -9256,7 +9248,7 @@
       <c r="F318" s="7"/>
       <c r="G318" s="7"/>
     </row>
-    <row r="319">
+    <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="7"/>
       <c r="B319" s="7" t="s">
         <v>22</v>
@@ -9269,7 +9261,7 @@
       <c r="F319" s="7"/>
       <c r="G319" s="7"/>
     </row>
-    <row r="320">
+    <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="7"/>
       <c r="B320" s="7" t="s">
         <v>23</v>
@@ -9282,7 +9274,7 @@
       <c r="F320" s="7"/>
       <c r="G320" s="7"/>
     </row>
-    <row r="321">
+    <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="7"/>
       <c r="B321" s="7" t="s">
         <v>25</v>
@@ -9295,7 +9287,7 @@
       <c r="F321" s="7"/>
       <c r="G321" s="7"/>
     </row>
-    <row r="322">
+    <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="7"/>
       <c r="B322" s="8" t="s">
         <v>26</v>
@@ -9308,7 +9300,7 @@
       <c r="F322" s="7"/>
       <c r="G322" s="7"/>
     </row>
-    <row r="323">
+    <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="7"/>
       <c r="B323" s="7" t="s">
         <v>28</v>
@@ -9321,7 +9313,7 @@
       <c r="F323" s="7"/>
       <c r="G323" s="7"/>
     </row>
-    <row r="324">
+    <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="7"/>
       <c r="B324" s="15" t="s">
         <v>30</v>
@@ -9334,11 +9326,11 @@
       <c r="F324" s="7"/>
       <c r="G324" s="7"/>
     </row>
-    <row r="325">
+    <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="28"/>
       <c r="C325" s="22"/>
     </row>
-    <row r="326">
+    <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="6" t="s">
         <v>87</v>
       </c>
@@ -9349,7 +9341,7 @@
       <c r="F326" s="7"/>
       <c r="G326" s="7"/>
     </row>
-    <row r="327">
+    <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="7"/>
       <c r="B327" s="7" t="s">
         <v>10</v>
@@ -9362,7 +9354,7 @@
       <c r="F327" s="7"/>
       <c r="G327" s="7"/>
     </row>
-    <row r="328">
+    <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="7"/>
       <c r="B328" s="7" t="s">
         <v>12</v>
@@ -9375,7 +9367,7 @@
       <c r="F328" s="7"/>
       <c r="G328" s="7"/>
     </row>
-    <row r="329">
+    <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="8"/>
       <c r="B329" s="8" t="s">
         <v>2</v>
@@ -9390,7 +9382,7 @@
       </c>
       <c r="G329" s="10"/>
     </row>
-    <row r="330">
+    <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="7"/>
       <c r="B330" s="8" t="s">
         <v>16</v>
@@ -9405,7 +9397,7 @@
       </c>
       <c r="G330" s="7"/>
     </row>
-    <row r="331">
+    <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="7"/>
       <c r="B331" s="7" t="s">
         <v>19</v>
@@ -9418,7 +9410,7 @@
       <c r="F331" s="7"/>
       <c r="G331" s="7"/>
     </row>
-    <row r="332">
+    <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="7"/>
       <c r="B332" s="7" t="s">
         <v>20</v>
@@ -9431,7 +9423,7 @@
       <c r="F332" s="7"/>
       <c r="G332" s="7"/>
     </row>
-    <row r="333">
+    <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="7"/>
       <c r="B333" s="7" t="s">
         <v>22</v>
@@ -9444,7 +9436,7 @@
       <c r="F333" s="7"/>
       <c r="G333" s="7"/>
     </row>
-    <row r="334">
+    <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="7"/>
       <c r="B334" s="7" t="s">
         <v>23</v>
@@ -9457,7 +9449,7 @@
       <c r="F334" s="7"/>
       <c r="G334" s="7"/>
     </row>
-    <row r="335">
+    <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="7"/>
       <c r="B335" s="7" t="s">
         <v>25</v>
@@ -9470,7 +9462,7 @@
       <c r="F335" s="7"/>
       <c r="G335" s="7"/>
     </row>
-    <row r="336">
+    <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="7"/>
       <c r="B336" s="8" t="s">
         <v>26</v>
@@ -9483,7 +9475,7 @@
       <c r="F336" s="7"/>
       <c r="G336" s="7"/>
     </row>
-    <row r="337">
+    <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="7"/>
       <c r="B337" s="7" t="s">
         <v>28</v>
@@ -9496,7 +9488,7 @@
       <c r="F337" s="7"/>
       <c r="G337" s="7"/>
     </row>
-    <row r="338">
+    <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="7"/>
       <c r="B338" s="15" t="s">
         <v>30</v>
@@ -9509,7 +9501,7 @@
       <c r="F338" s="7"/>
       <c r="G338" s="7"/>
     </row>
-    <row r="339">
+    <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="7"/>
       <c r="B339" s="7"/>
       <c r="C339" s="10"/>
@@ -9518,7 +9510,7 @@
       <c r="F339" s="7"/>
       <c r="G339" s="7"/>
     </row>
-    <row r="340">
+    <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="6" t="s">
         <v>90</v>
       </c>
@@ -9529,7 +9521,7 @@
       <c r="F340" s="7"/>
       <c r="G340" s="7"/>
     </row>
-    <row r="341">
+    <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="7"/>
       <c r="B341" s="7" t="s">
         <v>10</v>
@@ -9542,7 +9534,7 @@
       <c r="F341" s="7"/>
       <c r="G341" s="7"/>
     </row>
-    <row r="342">
+    <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="7"/>
       <c r="B342" s="7" t="s">
         <v>12</v>
@@ -9555,7 +9547,7 @@
       <c r="F342" s="7"/>
       <c r="G342" s="7"/>
     </row>
-    <row r="343">
+    <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="8"/>
       <c r="B343" s="8" t="s">
         <v>2</v>
@@ -9570,7 +9562,7 @@
       </c>
       <c r="G343" s="7"/>
     </row>
-    <row r="344">
+    <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="7"/>
       <c r="B344" s="8" t="s">
         <v>16</v>
@@ -9585,7 +9577,7 @@
       </c>
       <c r="G344" s="10"/>
     </row>
-    <row r="345">
+    <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="7"/>
       <c r="B345" s="7" t="s">
         <v>19</v>
@@ -9598,7 +9590,7 @@
       <c r="F345" s="7"/>
       <c r="G345" s="7"/>
     </row>
-    <row r="346">
+    <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="7"/>
       <c r="B346" s="7" t="s">
         <v>20</v>
@@ -9611,7 +9603,7 @@
       <c r="F346" s="7"/>
       <c r="G346" s="7"/>
     </row>
-    <row r="347">
+    <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="7"/>
       <c r="B347" s="7" t="s">
         <v>22</v>
@@ -9624,7 +9616,7 @@
       <c r="F347" s="7"/>
       <c r="G347" s="7"/>
     </row>
-    <row r="348">
+    <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="7"/>
       <c r="B348" s="7" t="s">
         <v>23</v>
@@ -9637,7 +9629,7 @@
       <c r="F348" s="7"/>
       <c r="G348" s="7"/>
     </row>
-    <row r="349">
+    <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="7"/>
       <c r="B349" s="7" t="s">
         <v>25</v>
@@ -9650,7 +9642,7 @@
       <c r="F349" s="7"/>
       <c r="G349" s="7"/>
     </row>
-    <row r="350">
+    <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="7"/>
       <c r="B350" s="8" t="s">
         <v>26</v>
@@ -9663,7 +9655,7 @@
       <c r="F350" s="7"/>
       <c r="G350" s="7"/>
     </row>
-    <row r="351">
+    <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="7"/>
       <c r="B351" s="7" t="s">
         <v>28</v>
@@ -9676,7 +9668,7 @@
       <c r="F351" s="7"/>
       <c r="G351" s="7"/>
     </row>
-    <row r="352">
+    <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="7"/>
       <c r="B352" s="15" t="s">
         <v>30</v>
@@ -9689,7 +9681,7 @@
       <c r="F352" s="7"/>
       <c r="G352" s="7"/>
     </row>
-    <row r="353">
+    <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="7"/>
       <c r="B353" s="7"/>
       <c r="C353" s="7"/>
@@ -9698,7 +9690,7 @@
       <c r="F353" s="7"/>
       <c r="G353" s="7"/>
     </row>
-    <row r="354">
+    <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="6" t="s">
         <v>92</v>
       </c>
@@ -9709,7 +9701,7 @@
       <c r="F354" s="7"/>
       <c r="G354" s="7"/>
     </row>
-    <row r="355">
+    <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="7"/>
       <c r="B355" s="7" t="s">
         <v>10</v>
@@ -9722,7 +9714,7 @@
       <c r="F355" s="7"/>
       <c r="G355" s="7"/>
     </row>
-    <row r="356">
+    <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="7"/>
       <c r="B356" s="7" t="s">
         <v>12</v>
@@ -9735,7 +9727,7 @@
       <c r="F356" s="7"/>
       <c r="G356" s="7"/>
     </row>
-    <row r="357">
+    <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="8"/>
       <c r="B357" s="8" t="s">
         <v>2</v>
@@ -9748,7 +9740,7 @@
       <c r="F357" s="10"/>
       <c r="G357" s="7"/>
     </row>
-    <row r="358">
+    <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="7"/>
       <c r="B358" s="7" t="s">
         <v>19</v>
@@ -9761,7 +9753,7 @@
       <c r="F358" s="7"/>
       <c r="G358" s="7"/>
     </row>
-    <row r="359">
+    <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="7"/>
       <c r="B359" s="7" t="s">
         <v>20</v>
@@ -9774,7 +9766,7 @@
       <c r="F359" s="7"/>
       <c r="G359" s="7"/>
     </row>
-    <row r="360">
+    <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="7"/>
       <c r="B360" s="7" t="s">
         <v>22</v>
@@ -9787,7 +9779,7 @@
       <c r="F360" s="7"/>
       <c r="G360" s="7"/>
     </row>
-    <row r="361">
+    <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="7"/>
       <c r="B361" s="7" t="s">
         <v>23</v>
@@ -9800,7 +9792,7 @@
       <c r="F361" s="7"/>
       <c r="G361" s="7"/>
     </row>
-    <row r="362">
+    <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="7"/>
       <c r="B362" s="7" t="s">
         <v>25</v>
@@ -9813,7 +9805,7 @@
       <c r="F362" s="7"/>
       <c r="G362" s="7"/>
     </row>
-    <row r="363">
+    <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="7"/>
       <c r="B363" s="8" t="s">
         <v>26</v>
@@ -9826,7 +9818,7 @@
       <c r="F363" s="7"/>
       <c r="G363" s="7"/>
     </row>
-    <row r="364">
+    <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="7"/>
       <c r="B364" s="7" t="s">
         <v>28</v>
@@ -9839,7 +9831,7 @@
       <c r="F364" s="7"/>
       <c r="G364" s="7"/>
     </row>
-    <row r="365">
+    <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="7"/>
       <c r="B365" s="15" t="s">
         <v>30</v>
@@ -9852,7 +9844,7 @@
       <c r="F365" s="7"/>
       <c r="G365" s="7"/>
     </row>
-    <row r="366">
+    <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="7"/>
       <c r="B366" s="7"/>
       <c r="C366" s="7"/>
@@ -9861,7 +9853,7 @@
       <c r="F366" s="7"/>
       <c r="G366" s="7"/>
     </row>
-    <row r="367">
+    <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="6" t="s">
         <v>94</v>
       </c>
@@ -9872,7 +9864,7 @@
       <c r="F367" s="7"/>
       <c r="G367" s="7"/>
     </row>
-    <row r="368">
+    <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="7"/>
       <c r="B368" s="7" t="s">
         <v>10</v>
@@ -9885,7 +9877,7 @@
       <c r="F368" s="7"/>
       <c r="G368" s="7"/>
     </row>
-    <row r="369">
+    <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="7"/>
       <c r="B369" s="7" t="s">
         <v>12</v>
@@ -9898,7 +9890,7 @@
       <c r="F369" s="7"/>
       <c r="G369" s="7"/>
     </row>
-    <row r="370">
+    <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="8"/>
       <c r="B370" s="8" t="s">
         <v>2</v>
@@ -9911,7 +9903,7 @@
       <c r="F370" s="7"/>
       <c r="G370" s="7"/>
     </row>
-    <row r="371">
+    <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="7"/>
       <c r="B371" s="7" t="s">
         <v>19</v>
@@ -9924,7 +9916,7 @@
       <c r="F371" s="7"/>
       <c r="G371" s="7"/>
     </row>
-    <row r="372">
+    <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="7"/>
       <c r="B372" s="7" t="s">
         <v>20</v>
@@ -9937,7 +9929,7 @@
       <c r="F372" s="7"/>
       <c r="G372" s="7"/>
     </row>
-    <row r="373">
+    <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="7"/>
       <c r="B373" s="7" t="s">
         <v>22</v>
@@ -9950,7 +9942,7 @@
       <c r="F373" s="7"/>
       <c r="G373" s="7"/>
     </row>
-    <row r="374">
+    <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="7"/>
       <c r="B374" s="7" t="s">
         <v>23</v>
@@ -9963,7 +9955,7 @@
       <c r="F374" s="7"/>
       <c r="G374" s="7"/>
     </row>
-    <row r="375">
+    <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="7"/>
       <c r="B375" s="7" t="s">
         <v>25</v>
@@ -9976,7 +9968,7 @@
       <c r="F375" s="7"/>
       <c r="G375" s="7"/>
     </row>
-    <row r="376">
+    <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="7"/>
       <c r="B376" s="8" t="s">
         <v>26</v>
@@ -9989,7 +9981,7 @@
       <c r="F376" s="7"/>
       <c r="G376" s="7"/>
     </row>
-    <row r="377">
+    <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="7"/>
       <c r="B377" s="7" t="s">
         <v>28</v>
@@ -10002,7 +9994,7 @@
       <c r="F377" s="7"/>
       <c r="G377" s="7"/>
     </row>
-    <row r="378">
+    <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="7"/>
       <c r="B378" s="15" t="s">
         <v>30</v>
@@ -10015,11 +10007,11 @@
       <c r="F378" s="7"/>
       <c r="G378" s="7"/>
     </row>
-    <row r="379">
+    <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="28"/>
       <c r="C379" s="22"/>
     </row>
-    <row r="380">
+    <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="6" t="s">
         <v>96</v>
       </c>
@@ -10030,7 +10022,7 @@
       <c r="F380" s="7"/>
       <c r="G380" s="7"/>
     </row>
-    <row r="381">
+    <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="7"/>
       <c r="B381" s="7" t="s">
         <v>10</v>
@@ -10043,7 +10035,7 @@
       <c r="F381" s="7"/>
       <c r="G381" s="7"/>
     </row>
-    <row r="382">
+    <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="7"/>
       <c r="B382" s="7" t="s">
         <v>12</v>
@@ -10056,7 +10048,7 @@
       <c r="F382" s="7"/>
       <c r="G382" s="7"/>
     </row>
-    <row r="383">
+    <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="8"/>
       <c r="B383" s="8" t="s">
         <v>2</v>
@@ -10071,7 +10063,7 @@
       </c>
       <c r="G383" s="10"/>
     </row>
-    <row r="384">
+    <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="7"/>
       <c r="B384" s="8" t="s">
         <v>16</v>
@@ -10086,7 +10078,7 @@
       </c>
       <c r="G384" s="7"/>
     </row>
-    <row r="385">
+    <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="7"/>
       <c r="B385" s="7" t="s">
         <v>19</v>
@@ -10099,7 +10091,7 @@
       <c r="F385" s="7"/>
       <c r="G385" s="7"/>
     </row>
-    <row r="386">
+    <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="7"/>
       <c r="B386" s="7" t="s">
         <v>20</v>
@@ -10112,7 +10104,7 @@
       <c r="F386" s="7"/>
       <c r="G386" s="7"/>
     </row>
-    <row r="387">
+    <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="7"/>
       <c r="B387" s="7" t="s">
         <v>22</v>
@@ -10125,7 +10117,7 @@
       <c r="F387" s="7"/>
       <c r="G387" s="7"/>
     </row>
-    <row r="388">
+    <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="7"/>
       <c r="B388" s="7" t="s">
         <v>23</v>
@@ -10138,7 +10130,7 @@
       <c r="F388" s="7"/>
       <c r="G388" s="7"/>
     </row>
-    <row r="389">
+    <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="7"/>
       <c r="B389" s="7" t="s">
         <v>25</v>
@@ -10151,7 +10143,7 @@
       <c r="F389" s="7"/>
       <c r="G389" s="7"/>
     </row>
-    <row r="390">
+    <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="7"/>
       <c r="B390" s="8" t="s">
         <v>26</v>
@@ -10164,7 +10156,7 @@
       <c r="F390" s="7"/>
       <c r="G390" s="7"/>
     </row>
-    <row r="391">
+    <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="7"/>
       <c r="B391" s="7" t="s">
         <v>28</v>
@@ -10177,7 +10169,7 @@
       <c r="F391" s="7"/>
       <c r="G391" s="7"/>
     </row>
-    <row r="392">
+    <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="7"/>
       <c r="B392" s="15" t="s">
         <v>30</v>
@@ -10190,7 +10182,7 @@
       <c r="F392" s="7"/>
       <c r="G392" s="7"/>
     </row>
-    <row r="393">
+    <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="7"/>
       <c r="B393" s="7"/>
       <c r="C393" s="10"/>
@@ -10199,7 +10191,7 @@
       <c r="F393" s="7"/>
       <c r="G393" s="7"/>
     </row>
-    <row r="394">
+    <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="6" t="s">
         <v>99</v>
       </c>
@@ -10210,7 +10202,7 @@
       <c r="F394" s="7"/>
       <c r="G394" s="7"/>
     </row>
-    <row r="395">
+    <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="7"/>
       <c r="B395" s="7" t="s">
         <v>10</v>
@@ -10223,7 +10215,7 @@
       <c r="F395" s="7"/>
       <c r="G395" s="7"/>
     </row>
-    <row r="396">
+    <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="7"/>
       <c r="B396" s="7" t="s">
         <v>12</v>
@@ -10236,7 +10228,7 @@
       <c r="F396" s="7"/>
       <c r="G396" s="7"/>
     </row>
-    <row r="397">
+    <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="8"/>
       <c r="B397" s="8" t="s">
         <v>2</v>
@@ -10251,7 +10243,7 @@
       </c>
       <c r="G397" s="7"/>
     </row>
-    <row r="398">
+    <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="7"/>
       <c r="B398" s="8" t="s">
         <v>16</v>
@@ -10266,7 +10258,7 @@
       </c>
       <c r="G398" s="10"/>
     </row>
-    <row r="399">
+    <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="7"/>
       <c r="B399" s="7" t="s">
         <v>19</v>
@@ -10279,7 +10271,7 @@
       <c r="F399" s="7"/>
       <c r="G399" s="7"/>
     </row>
-    <row r="400">
+    <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="7"/>
       <c r="B400" s="7" t="s">
         <v>20</v>
@@ -10292,7 +10284,7 @@
       <c r="F400" s="7"/>
       <c r="G400" s="7"/>
     </row>
-    <row r="401">
+    <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="7"/>
       <c r="B401" s="7" t="s">
         <v>22</v>
@@ -10305,7 +10297,7 @@
       <c r="F401" s="7"/>
       <c r="G401" s="7"/>
     </row>
-    <row r="402">
+    <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="7"/>
       <c r="B402" s="7" t="s">
         <v>23</v>
@@ -10318,7 +10310,7 @@
       <c r="F402" s="7"/>
       <c r="G402" s="7"/>
     </row>
-    <row r="403">
+    <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="7"/>
       <c r="B403" s="7" t="s">
         <v>25</v>
@@ -10331,7 +10323,7 @@
       <c r="F403" s="7"/>
       <c r="G403" s="7"/>
     </row>
-    <row r="404">
+    <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="7"/>
       <c r="B404" s="8" t="s">
         <v>26</v>
@@ -10344,7 +10336,7 @@
       <c r="F404" s="7"/>
       <c r="G404" s="7"/>
     </row>
-    <row r="405">
+    <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="7"/>
       <c r="B405" s="7" t="s">
         <v>28</v>
@@ -10357,7 +10349,7 @@
       <c r="F405" s="7"/>
       <c r="G405" s="7"/>
     </row>
-    <row r="406">
+    <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="7"/>
       <c r="B406" s="15" t="s">
         <v>30</v>
@@ -10370,7 +10362,7 @@
       <c r="F406" s="7"/>
       <c r="G406" s="7"/>
     </row>
-    <row r="407">
+    <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="7"/>
       <c r="B407" s="7"/>
       <c r="C407" s="7"/>
@@ -10379,7 +10371,7 @@
       <c r="F407" s="7"/>
       <c r="G407" s="7"/>
     </row>
-    <row r="408">
+    <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="6" t="s">
         <v>101</v>
       </c>
@@ -10390,7 +10382,7 @@
       <c r="F408" s="7"/>
       <c r="G408" s="7"/>
     </row>
-    <row r="409">
+    <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="7"/>
       <c r="B409" s="7" t="s">
         <v>10</v>
@@ -10403,7 +10395,7 @@
       <c r="F409" s="7"/>
       <c r="G409" s="7"/>
     </row>
-    <row r="410">
+    <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="7"/>
       <c r="B410" s="7" t="s">
         <v>12</v>
@@ -10416,7 +10408,7 @@
       <c r="F410" s="7"/>
       <c r="G410" s="7"/>
     </row>
-    <row r="411">
+    <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="8"/>
       <c r="B411" s="8" t="s">
         <v>2</v>
@@ -10429,7 +10421,7 @@
       <c r="F411" s="10"/>
       <c r="G411" s="7"/>
     </row>
-    <row r="412">
+    <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="7"/>
       <c r="B412" s="7" t="s">
         <v>19</v>
@@ -10442,7 +10434,7 @@
       <c r="F412" s="7"/>
       <c r="G412" s="7"/>
     </row>
-    <row r="413">
+    <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="7"/>
       <c r="B413" s="7" t="s">
         <v>20</v>
@@ -10455,7 +10447,7 @@
       <c r="F413" s="7"/>
       <c r="G413" s="7"/>
     </row>
-    <row r="414">
+    <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="7"/>
       <c r="B414" s="7" t="s">
         <v>22</v>
@@ -10468,7 +10460,7 @@
       <c r="F414" s="7"/>
       <c r="G414" s="7"/>
     </row>
-    <row r="415">
+    <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="7"/>
       <c r="B415" s="7" t="s">
         <v>23</v>
@@ -10481,7 +10473,7 @@
       <c r="F415" s="7"/>
       <c r="G415" s="7"/>
     </row>
-    <row r="416">
+    <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="7"/>
       <c r="B416" s="7" t="s">
         <v>25</v>
@@ -10494,7 +10486,7 @@
       <c r="F416" s="7"/>
       <c r="G416" s="7"/>
     </row>
-    <row r="417">
+    <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="7"/>
       <c r="B417" s="8" t="s">
         <v>26</v>
@@ -10507,7 +10499,7 @@
       <c r="F417" s="7"/>
       <c r="G417" s="7"/>
     </row>
-    <row r="418">
+    <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="7"/>
       <c r="B418" s="7" t="s">
         <v>28</v>
@@ -10520,7 +10512,7 @@
       <c r="F418" s="7"/>
       <c r="G418" s="7"/>
     </row>
-    <row r="419">
+    <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="7"/>
       <c r="B419" s="15" t="s">
         <v>30</v>
@@ -10533,7 +10525,7 @@
       <c r="F419" s="7"/>
       <c r="G419" s="7"/>
     </row>
-    <row r="420">
+    <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="7"/>
       <c r="B420" s="7"/>
       <c r="C420" s="7"/>
@@ -10542,7 +10534,7 @@
       <c r="F420" s="7"/>
       <c r="G420" s="7"/>
     </row>
-    <row r="421">
+    <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="6" t="s">
         <v>103</v>
       </c>
@@ -10553,7 +10545,7 @@
       <c r="F421" s="7"/>
       <c r="G421" s="7"/>
     </row>
-    <row r="422">
+    <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="7"/>
       <c r="B422" s="7" t="s">
         <v>10</v>
@@ -10566,7 +10558,7 @@
       <c r="F422" s="7"/>
       <c r="G422" s="7"/>
     </row>
-    <row r="423">
+    <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="7"/>
       <c r="B423" s="7" t="s">
         <v>12</v>
@@ -10579,7 +10571,7 @@
       <c r="F423" s="7"/>
       <c r="G423" s="7"/>
     </row>
-    <row r="424">
+    <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="8"/>
       <c r="B424" s="8" t="s">
         <v>2</v>
@@ -10592,7 +10584,7 @@
       <c r="F424" s="7"/>
       <c r="G424" s="7"/>
     </row>
-    <row r="425">
+    <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="7"/>
       <c r="B425" s="7" t="s">
         <v>19</v>
@@ -10605,7 +10597,7 @@
       <c r="F425" s="7"/>
       <c r="G425" s="7"/>
     </row>
-    <row r="426">
+    <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="7"/>
       <c r="B426" s="7" t="s">
         <v>20</v>
@@ -10618,7 +10610,7 @@
       <c r="F426" s="7"/>
       <c r="G426" s="7"/>
     </row>
-    <row r="427">
+    <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="7"/>
       <c r="B427" s="7" t="s">
         <v>22</v>
@@ -10631,7 +10623,7 @@
       <c r="F427" s="7"/>
       <c r="G427" s="7"/>
     </row>
-    <row r="428">
+    <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="7"/>
       <c r="B428" s="7" t="s">
         <v>23</v>
@@ -10644,7 +10636,7 @@
       <c r="F428" s="7"/>
       <c r="G428" s="7"/>
     </row>
-    <row r="429">
+    <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="7"/>
       <c r="B429" s="7" t="s">
         <v>25</v>
@@ -10657,7 +10649,7 @@
       <c r="F429" s="7"/>
       <c r="G429" s="7"/>
     </row>
-    <row r="430">
+    <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="7"/>
       <c r="B430" s="8" t="s">
         <v>26</v>
@@ -10670,7 +10662,7 @@
       <c r="F430" s="7"/>
       <c r="G430" s="7"/>
     </row>
-    <row r="431">
+    <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="7"/>
       <c r="B431" s="7" t="s">
         <v>28</v>
@@ -10683,7 +10675,7 @@
       <c r="F431" s="7"/>
       <c r="G431" s="7"/>
     </row>
-    <row r="432">
+    <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="7"/>
       <c r="B432" s="15" t="s">
         <v>30</v>
@@ -10696,11 +10688,11 @@
       <c r="F432" s="7"/>
       <c r="G432" s="7"/>
     </row>
-    <row r="433">
+    <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="28"/>
       <c r="C433" s="22"/>
     </row>
-    <row r="434">
+    <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="6" t="s">
         <v>105</v>
       </c>
@@ -10711,7 +10703,7 @@
       <c r="F434" s="7"/>
       <c r="G434" s="7"/>
     </row>
-    <row r="435">
+    <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="7"/>
       <c r="B435" s="7" t="s">
         <v>10</v>
@@ -10724,7 +10716,7 @@
       <c r="F435" s="7"/>
       <c r="G435" s="7"/>
     </row>
-    <row r="436">
+    <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="7"/>
       <c r="B436" s="7" t="s">
         <v>12</v>
@@ -10737,7 +10729,7 @@
       <c r="F436" s="7"/>
       <c r="G436" s="7"/>
     </row>
-    <row r="437">
+    <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="8"/>
       <c r="B437" s="8" t="s">
         <v>2</v>
@@ -10752,7 +10744,7 @@
       </c>
       <c r="G437" s="10"/>
     </row>
-    <row r="438">
+    <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="7"/>
       <c r="B438" s="8" t="s">
         <v>16</v>
@@ -10767,7 +10759,7 @@
       </c>
       <c r="G438" s="7"/>
     </row>
-    <row r="439">
+    <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="7"/>
       <c r="B439" s="7" t="s">
         <v>19</v>
@@ -10780,7 +10772,7 @@
       <c r="F439" s="7"/>
       <c r="G439" s="7"/>
     </row>
-    <row r="440">
+    <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="7"/>
       <c r="B440" s="7" t="s">
         <v>20</v>
@@ -10793,7 +10785,7 @@
       <c r="F440" s="7"/>
       <c r="G440" s="7"/>
     </row>
-    <row r="441">
+    <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="7"/>
       <c r="B441" s="7" t="s">
         <v>22</v>
@@ -10806,7 +10798,7 @@
       <c r="F441" s="7"/>
       <c r="G441" s="7"/>
     </row>
-    <row r="442">
+    <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="7"/>
       <c r="B442" s="7" t="s">
         <v>23</v>
@@ -10819,7 +10811,7 @@
       <c r="F442" s="7"/>
       <c r="G442" s="7"/>
     </row>
-    <row r="443">
+    <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="7"/>
       <c r="B443" s="7" t="s">
         <v>25</v>
@@ -10832,7 +10824,7 @@
       <c r="F443" s="7"/>
       <c r="G443" s="7"/>
     </row>
-    <row r="444">
+    <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="7"/>
       <c r="B444" s="8" t="s">
         <v>26</v>
@@ -10845,7 +10837,7 @@
       <c r="F444" s="7"/>
       <c r="G444" s="7"/>
     </row>
-    <row r="445">
+    <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="7"/>
       <c r="B445" s="7" t="s">
         <v>28</v>
@@ -10858,7 +10850,7 @@
       <c r="F445" s="7"/>
       <c r="G445" s="7"/>
     </row>
-    <row r="446">
+    <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="7"/>
       <c r="B446" s="15" t="s">
         <v>30</v>
@@ -10871,7 +10863,7 @@
       <c r="F446" s="7"/>
       <c r="G446" s="7"/>
     </row>
-    <row r="447">
+    <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="7"/>
       <c r="B447" s="7"/>
       <c r="C447" s="10"/>
@@ -10880,7 +10872,7 @@
       <c r="F447" s="7"/>
       <c r="G447" s="7"/>
     </row>
-    <row r="448">
+    <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="6" t="s">
         <v>108</v>
       </c>
@@ -10891,7 +10883,7 @@
       <c r="F448" s="7"/>
       <c r="G448" s="7"/>
     </row>
-    <row r="449">
+    <row r="449" ht="15.75" customHeight="1">
       <c r="A449" s="7"/>
       <c r="B449" s="7" t="s">
         <v>10</v>
@@ -10904,7 +10896,7 @@
       <c r="F449" s="7"/>
       <c r="G449" s="7"/>
     </row>
-    <row r="450">
+    <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="7"/>
       <c r="B450" s="7" t="s">
         <v>12</v>
@@ -10917,7 +10909,7 @@
       <c r="F450" s="7"/>
       <c r="G450" s="7"/>
     </row>
-    <row r="451">
+    <row r="451" ht="15.75" customHeight="1">
       <c r="A451" s="8"/>
       <c r="B451" s="8" t="s">
         <v>2</v>
@@ -10932,7 +10924,7 @@
       </c>
       <c r="G451" s="7"/>
     </row>
-    <row r="452">
+    <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="7"/>
       <c r="B452" s="8" t="s">
         <v>16</v>
@@ -10947,7 +10939,7 @@
       </c>
       <c r="G452" s="10"/>
     </row>
-    <row r="453">
+    <row r="453" ht="15.75" customHeight="1">
       <c r="A453" s="7"/>
       <c r="B453" s="7" t="s">
         <v>19</v>
@@ -10960,7 +10952,7 @@
       <c r="F453" s="7"/>
       <c r="G453" s="7"/>
     </row>
-    <row r="454">
+    <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="7"/>
       <c r="B454" s="7" t="s">
         <v>20</v>
@@ -10973,7 +10965,7 @@
       <c r="F454" s="7"/>
       <c r="G454" s="7"/>
     </row>
-    <row r="455">
+    <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="7"/>
       <c r="B455" s="7" t="s">
         <v>22</v>
@@ -10986,7 +10978,7 @@
       <c r="F455" s="7"/>
       <c r="G455" s="7"/>
     </row>
-    <row r="456">
+    <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="7"/>
       <c r="B456" s="7" t="s">
         <v>23</v>
@@ -10999,7 +10991,7 @@
       <c r="F456" s="7"/>
       <c r="G456" s="7"/>
     </row>
-    <row r="457">
+    <row r="457" ht="15.75" customHeight="1">
       <c r="A457" s="7"/>
       <c r="B457" s="7" t="s">
         <v>25</v>
@@ -11012,7 +11004,7 @@
       <c r="F457" s="7"/>
       <c r="G457" s="7"/>
     </row>
-    <row r="458">
+    <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="7"/>
       <c r="B458" s="8" t="s">
         <v>26</v>
@@ -11025,7 +11017,7 @@
       <c r="F458" s="7"/>
       <c r="G458" s="7"/>
     </row>
-    <row r="459">
+    <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="7"/>
       <c r="B459" s="7" t="s">
         <v>28</v>
@@ -11038,7 +11030,7 @@
       <c r="F459" s="7"/>
       <c r="G459" s="7"/>
     </row>
-    <row r="460">
+    <row r="460" ht="15.75" customHeight="1">
       <c r="A460" s="7"/>
       <c r="B460" s="15" t="s">
         <v>30</v>
@@ -11051,7 +11043,7 @@
       <c r="F460" s="7"/>
       <c r="G460" s="7"/>
     </row>
-    <row r="461">
+    <row r="461" ht="15.75" customHeight="1">
       <c r="A461" s="7"/>
       <c r="B461" s="7"/>
       <c r="C461" s="7"/>
@@ -11060,7 +11052,7 @@
       <c r="F461" s="7"/>
       <c r="G461" s="7"/>
     </row>
-    <row r="462">
+    <row r="462" ht="15.75" customHeight="1">
       <c r="A462" s="6" t="s">
         <v>110</v>
       </c>
@@ -11071,7 +11063,7 @@
       <c r="F462" s="7"/>
       <c r="G462" s="7"/>
     </row>
-    <row r="463">
+    <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="7"/>
       <c r="B463" s="7" t="s">
         <v>10</v>
@@ -11084,7 +11076,7 @@
       <c r="F463" s="7"/>
       <c r="G463" s="7"/>
     </row>
-    <row r="464">
+    <row r="464" ht="15.75" customHeight="1">
       <c r="A464" s="7"/>
       <c r="B464" s="7" t="s">
         <v>12</v>
@@ -11097,7 +11089,7 @@
       <c r="F464" s="7"/>
       <c r="G464" s="7"/>
     </row>
-    <row r="465">
+    <row r="465" ht="15.75" customHeight="1">
       <c r="A465" s="8"/>
       <c r="B465" s="8" t="s">
         <v>2</v>
@@ -11110,7 +11102,7 @@
       <c r="F465" s="10"/>
       <c r="G465" s="7"/>
     </row>
-    <row r="466">
+    <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="7"/>
       <c r="B466" s="7" t="s">
         <v>19</v>
@@ -11123,7 +11115,7 @@
       <c r="F466" s="7"/>
       <c r="G466" s="7"/>
     </row>
-    <row r="467">
+    <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="7"/>
       <c r="B467" s="7" t="s">
         <v>20</v>
@@ -11136,7 +11128,7 @@
       <c r="F467" s="7"/>
       <c r="G467" s="7"/>
     </row>
-    <row r="468">
+    <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="7"/>
       <c r="B468" s="7" t="s">
         <v>22</v>
@@ -11149,7 +11141,7 @@
       <c r="F468" s="7"/>
       <c r="G468" s="7"/>
     </row>
-    <row r="469">
+    <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="7"/>
       <c r="B469" s="7" t="s">
         <v>23</v>
@@ -11162,7 +11154,7 @@
       <c r="F469" s="7"/>
       <c r="G469" s="7"/>
     </row>
-    <row r="470">
+    <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="7"/>
       <c r="B470" s="7" t="s">
         <v>25</v>
@@ -11175,7 +11167,7 @@
       <c r="F470" s="7"/>
       <c r="G470" s="7"/>
     </row>
-    <row r="471">
+    <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="7"/>
       <c r="B471" s="8" t="s">
         <v>26</v>
@@ -11188,7 +11180,7 @@
       <c r="F471" s="7"/>
       <c r="G471" s="7"/>
     </row>
-    <row r="472">
+    <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="7"/>
       <c r="B472" s="7" t="s">
         <v>28</v>
@@ -11201,7 +11193,7 @@
       <c r="F472" s="7"/>
       <c r="G472" s="7"/>
     </row>
-    <row r="473">
+    <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="7"/>
       <c r="B473" s="15" t="s">
         <v>30</v>
@@ -11214,7 +11206,7 @@
       <c r="F473" s="7"/>
       <c r="G473" s="7"/>
     </row>
-    <row r="474">
+    <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="7"/>
       <c r="B474" s="7"/>
       <c r="C474" s="7"/>
@@ -11223,7 +11215,7 @@
       <c r="F474" s="7"/>
       <c r="G474" s="7"/>
     </row>
-    <row r="475">
+    <row r="475" ht="15.75" customHeight="1">
       <c r="A475" s="6" t="s">
         <v>112</v>
       </c>
@@ -11234,7 +11226,7 @@
       <c r="F475" s="7"/>
       <c r="G475" s="7"/>
     </row>
-    <row r="476">
+    <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="7"/>
       <c r="B476" s="7" t="s">
         <v>10</v>
@@ -11247,7 +11239,7 @@
       <c r="F476" s="7"/>
       <c r="G476" s="7"/>
     </row>
-    <row r="477">
+    <row r="477" ht="15.75" customHeight="1">
       <c r="A477" s="7"/>
       <c r="B477" s="7" t="s">
         <v>12</v>
@@ -11260,7 +11252,7 @@
       <c r="F477" s="7"/>
       <c r="G477" s="7"/>
     </row>
-    <row r="478">
+    <row r="478" ht="15.75" customHeight="1">
       <c r="A478" s="8"/>
       <c r="B478" s="8" t="s">
         <v>2</v>
@@ -11273,7 +11265,7 @@
       <c r="F478" s="7"/>
       <c r="G478" s="7"/>
     </row>
-    <row r="479">
+    <row r="479" ht="15.75" customHeight="1">
       <c r="A479" s="7"/>
       <c r="B479" s="7" t="s">
         <v>19</v>
@@ -11286,12 +11278,12 @@
       <c r="F479" s="7"/>
       <c r="G479" s="7"/>
     </row>
-    <row r="480">
+    <row r="480" ht="15.75" customHeight="1">
       <c r="A480" s="7"/>
       <c r="B480" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C480" s="29" t="s">
+      <c r="C480" s="7" t="s">
         <v>113</v>
       </c>
       <c r="D480" s="7"/>
@@ -11299,7 +11291,7 @@
       <c r="F480" s="7"/>
       <c r="G480" s="7"/>
     </row>
-    <row r="481">
+    <row r="481" ht="15.75" customHeight="1">
       <c r="A481" s="7"/>
       <c r="B481" s="7" t="s">
         <v>22</v>
@@ -11312,7 +11304,7 @@
       <c r="F481" s="7"/>
       <c r="G481" s="7"/>
     </row>
-    <row r="482">
+    <row r="482" ht="15.75" customHeight="1">
       <c r="A482" s="7"/>
       <c r="B482" s="7" t="s">
         <v>23</v>
@@ -11325,7 +11317,7 @@
       <c r="F482" s="7"/>
       <c r="G482" s="7"/>
     </row>
-    <row r="483">
+    <row r="483" ht="15.75" customHeight="1">
       <c r="A483" s="7"/>
       <c r="B483" s="7" t="s">
         <v>25</v>
@@ -11338,7 +11330,7 @@
       <c r="F483" s="7"/>
       <c r="G483" s="7"/>
     </row>
-    <row r="484">
+    <row r="484" ht="15.75" customHeight="1">
       <c r="A484" s="7"/>
       <c r="B484" s="8" t="s">
         <v>26</v>
@@ -11351,7 +11343,7 @@
       <c r="F484" s="7"/>
       <c r="G484" s="7"/>
     </row>
-    <row r="485">
+    <row r="485" ht="15.75" customHeight="1">
       <c r="A485" s="7"/>
       <c r="B485" s="7" t="s">
         <v>28</v>
@@ -11364,7 +11356,7 @@
       <c r="F485" s="7"/>
       <c r="G485" s="7"/>
     </row>
-    <row r="486">
+    <row r="486" ht="15.75" customHeight="1">
       <c r="A486" s="7"/>
       <c r="B486" s="15" t="s">
         <v>30</v>
@@ -11377,11 +11369,11 @@
       <c r="F486" s="7"/>
       <c r="G486" s="7"/>
     </row>
-    <row r="487">
+    <row r="487" ht="15.75" customHeight="1">
       <c r="A487" s="28"/>
       <c r="C487" s="22"/>
     </row>
-    <row r="488">
+    <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="25" t="s">
         <v>114</v>
       </c>
@@ -11392,7 +11384,7 @@
       <c r="F488" s="2"/>
       <c r="G488" s="2"/>
     </row>
-    <row r="489">
+    <row r="489" ht="15.75" customHeight="1">
       <c r="A489" s="20"/>
       <c r="B489" s="2" t="s">
         <v>10</v>
@@ -11405,7 +11397,7 @@
       <c r="F489" s="2"/>
       <c r="G489" s="2"/>
     </row>
-    <row r="490">
+    <row r="490" ht="15.75" customHeight="1">
       <c r="A490" s="20"/>
       <c r="B490" s="2" t="s">
         <v>12</v>
@@ -11418,12 +11410,12 @@
       <c r="F490" s="2"/>
       <c r="G490" s="2"/>
     </row>
-    <row r="491">
+    <row r="491" ht="15.75" customHeight="1">
       <c r="A491" s="20"/>
       <c r="B491" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C491" s="30">
+      <c r="C491" s="29">
         <v>1.0</v>
       </c>
       <c r="D491" s="2"/>
@@ -11431,18 +11423,18 @@
       <c r="F491" s="2"/>
       <c r="G491" s="2"/>
     </row>
-    <row r="492">
+    <row r="492" ht="15.75" customHeight="1">
       <c r="A492" s="20"/>
       <c r="B492" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C492" s="30"/>
+      <c r="C492" s="29"/>
       <c r="D492" s="2"/>
       <c r="E492" s="2"/>
       <c r="F492" s="2"/>
       <c r="G492" s="2"/>
     </row>
-    <row r="493">
+    <row r="493" ht="15.75" customHeight="1">
       <c r="A493" s="20"/>
       <c r="B493" s="2" t="s">
         <v>20</v>
@@ -11455,7 +11447,7 @@
       <c r="F493" s="2"/>
       <c r="G493" s="2"/>
     </row>
-    <row r="494">
+    <row r="494" ht="15.75" customHeight="1">
       <c r="A494" s="20"/>
       <c r="B494" s="7" t="s">
         <v>117</v>
@@ -11468,7 +11460,7 @@
       <c r="F494" s="2"/>
       <c r="G494" s="2"/>
     </row>
-    <row r="495">
+    <row r="495" ht="15.75" customHeight="1">
       <c r="A495" s="20"/>
       <c r="B495" s="10" t="s">
         <v>119</v>
@@ -11481,16 +11473,16 @@
       <c r="F495" s="2"/>
       <c r="G495" s="2"/>
     </row>
-    <row r="496">
+    <row r="496" ht="15.75" customHeight="1">
       <c r="A496" s="20"/>
       <c r="B496" s="2"/>
-      <c r="C496" s="30"/>
+      <c r="C496" s="29"/>
       <c r="D496" s="2"/>
       <c r="E496" s="2"/>
       <c r="F496" s="2"/>
       <c r="G496" s="2"/>
     </row>
-    <row r="497">
+    <row r="497" ht="15.75" customHeight="1">
       <c r="A497" s="25" t="s">
         <v>121</v>
       </c>
@@ -11501,7 +11493,7 @@
       <c r="F497" s="2"/>
       <c r="G497" s="2"/>
     </row>
-    <row r="498">
+    <row r="498" ht="15.75" customHeight="1">
       <c r="A498" s="20"/>
       <c r="B498" s="2" t="s">
         <v>10</v>
@@ -11514,7 +11506,7 @@
       <c r="F498" s="2"/>
       <c r="G498" s="2"/>
     </row>
-    <row r="499">
+    <row r="499" ht="15.75" customHeight="1">
       <c r="A499" s="20"/>
       <c r="B499" s="2" t="s">
         <v>12</v>
@@ -11527,12 +11519,12 @@
       <c r="F499" s="2"/>
       <c r="G499" s="2"/>
     </row>
-    <row r="500">
+    <row r="500" ht="15.75" customHeight="1">
       <c r="A500" s="20"/>
       <c r="B500" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C500" s="30">
+      <c r="C500" s="29">
         <v>1.0</v>
       </c>
       <c r="D500" s="2"/>
@@ -11540,18 +11532,18 @@
       <c r="F500" s="2"/>
       <c r="G500" s="2"/>
     </row>
-    <row r="501">
+    <row r="501" ht="15.75" customHeight="1">
       <c r="A501" s="20"/>
       <c r="B501" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C501" s="30"/>
+      <c r="C501" s="29"/>
       <c r="D501" s="2"/>
       <c r="E501" s="2"/>
       <c r="F501" s="2"/>
       <c r="G501" s="2"/>
     </row>
-    <row r="502">
+    <row r="502" ht="15.75" customHeight="1">
       <c r="A502" s="20"/>
       <c r="B502" s="2" t="s">
         <v>20</v>
@@ -11564,7 +11556,7 @@
       <c r="F502" s="2"/>
       <c r="G502" s="2"/>
     </row>
-    <row r="503">
+    <row r="503" ht="15.75" customHeight="1">
       <c r="A503" s="20"/>
       <c r="B503" s="7" t="s">
         <v>117</v>
@@ -11577,7 +11569,7 @@
       <c r="F503" s="2"/>
       <c r="G503" s="2"/>
     </row>
-    <row r="504">
+    <row r="504" ht="15.75" customHeight="1">
       <c r="A504" s="20"/>
       <c r="B504" s="10" t="s">
         <v>119</v>
@@ -11590,16 +11582,16 @@
       <c r="F504" s="2"/>
       <c r="G504" s="2"/>
     </row>
-    <row r="505">
+    <row r="505" ht="15.75" customHeight="1">
       <c r="A505" s="20"/>
       <c r="B505" s="2"/>
-      <c r="C505" s="30"/>
+      <c r="C505" s="29"/>
       <c r="D505" s="2"/>
       <c r="E505" s="2"/>
       <c r="F505" s="2"/>
       <c r="G505" s="2"/>
     </row>
-    <row r="506">
+    <row r="506" ht="15.75" customHeight="1">
       <c r="A506" s="25" t="s">
         <v>123</v>
       </c>
@@ -11610,7 +11602,7 @@
       <c r="F506" s="2"/>
       <c r="G506" s="2"/>
     </row>
-    <row r="507">
+    <row r="507" ht="15.75" customHeight="1">
       <c r="A507" s="20"/>
       <c r="B507" s="2" t="s">
         <v>10</v>
@@ -11623,7 +11615,7 @@
       <c r="F507" s="2"/>
       <c r="G507" s="2"/>
     </row>
-    <row r="508">
+    <row r="508" ht="15.75" customHeight="1">
       <c r="A508" s="20"/>
       <c r="B508" s="2" t="s">
         <v>12</v>
@@ -11636,12 +11628,12 @@
       <c r="F508" s="2"/>
       <c r="G508" s="2"/>
     </row>
-    <row r="509">
+    <row r="509" ht="15.75" customHeight="1">
       <c r="A509" s="20"/>
       <c r="B509" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C509" s="30">
+      <c r="C509" s="29">
         <v>1.0</v>
       </c>
       <c r="D509" s="2"/>
@@ -11649,18 +11641,18 @@
       <c r="F509" s="2"/>
       <c r="G509" s="2"/>
     </row>
-    <row r="510">
+    <row r="510" ht="15.75" customHeight="1">
       <c r="A510" s="20"/>
       <c r="B510" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C510" s="30"/>
+      <c r="C510" s="29"/>
       <c r="D510" s="2"/>
       <c r="E510" s="2"/>
       <c r="F510" s="2"/>
       <c r="G510" s="2"/>
     </row>
-    <row r="511">
+    <row r="511" ht="15.75" customHeight="1">
       <c r="A511" s="20"/>
       <c r="B511" s="2" t="s">
         <v>20</v>
@@ -11673,7 +11665,7 @@
       <c r="F511" s="2"/>
       <c r="G511" s="2"/>
     </row>
-    <row r="512">
+    <row r="512" ht="15.75" customHeight="1">
       <c r="A512" s="20"/>
       <c r="B512" s="7" t="s">
         <v>117</v>
@@ -11686,7 +11678,7 @@
       <c r="F512" s="2"/>
       <c r="G512" s="2"/>
     </row>
-    <row r="513">
+    <row r="513" ht="15.75" customHeight="1">
       <c r="A513" s="20"/>
       <c r="B513" s="10" t="s">
         <v>119</v>
@@ -11699,16 +11691,16 @@
       <c r="F513" s="2"/>
       <c r="G513" s="2"/>
     </row>
-    <row r="514">
+    <row r="514" ht="15.75" customHeight="1">
       <c r="A514" s="20"/>
       <c r="B514" s="2"/>
-      <c r="C514" s="30"/>
+      <c r="C514" s="29"/>
       <c r="D514" s="2"/>
       <c r="E514" s="2"/>
       <c r="F514" s="2"/>
       <c r="G514" s="2"/>
     </row>
-    <row r="515">
+    <row r="515" ht="15.75" customHeight="1">
       <c r="A515" s="25" t="s">
         <v>125</v>
       </c>
@@ -11719,7 +11711,7 @@
       <c r="F515" s="2"/>
       <c r="G515" s="2"/>
     </row>
-    <row r="516">
+    <row r="516" ht="15.75" customHeight="1">
       <c r="A516" s="20"/>
       <c r="B516" s="2" t="s">
         <v>10</v>
@@ -11732,7 +11724,7 @@
       <c r="F516" s="2"/>
       <c r="G516" s="2"/>
     </row>
-    <row r="517">
+    <row r="517" ht="15.75" customHeight="1">
       <c r="A517" s="20"/>
       <c r="B517" s="2" t="s">
         <v>12</v>
@@ -11745,12 +11737,12 @@
       <c r="F517" s="2"/>
       <c r="G517" s="2"/>
     </row>
-    <row r="518">
+    <row r="518" ht="15.75" customHeight="1">
       <c r="A518" s="20"/>
       <c r="B518" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C518" s="30">
+      <c r="C518" s="29">
         <v>1.0</v>
       </c>
       <c r="D518" s="2"/>
@@ -11758,18 +11750,18 @@
       <c r="F518" s="2"/>
       <c r="G518" s="2"/>
     </row>
-    <row r="519">
+    <row r="519" ht="15.75" customHeight="1">
       <c r="A519" s="20"/>
       <c r="B519" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C519" s="30"/>
+      <c r="C519" s="29"/>
       <c r="D519" s="2"/>
       <c r="E519" s="2"/>
       <c r="F519" s="2"/>
       <c r="G519" s="2"/>
     </row>
-    <row r="520">
+    <row r="520" ht="15.75" customHeight="1">
       <c r="A520" s="20"/>
       <c r="B520" s="2" t="s">
         <v>20</v>
@@ -11782,7 +11774,7 @@
       <c r="F520" s="2"/>
       <c r="G520" s="2"/>
     </row>
-    <row r="521">
+    <row r="521" ht="15.75" customHeight="1">
       <c r="A521" s="20"/>
       <c r="B521" s="7" t="s">
         <v>117</v>
@@ -11795,7 +11787,7 @@
       <c r="F521" s="2"/>
       <c r="G521" s="2"/>
     </row>
-    <row r="522">
+    <row r="522" ht="15.75" customHeight="1">
       <c r="A522" s="20"/>
       <c r="B522" s="10" t="s">
         <v>119</v>
@@ -11808,16 +11800,16 @@
       <c r="F522" s="2"/>
       <c r="G522" s="2"/>
     </row>
-    <row r="523">
+    <row r="523" ht="15.75" customHeight="1">
       <c r="A523" s="20"/>
       <c r="B523" s="2"/>
-      <c r="C523" s="30"/>
+      <c r="C523" s="29"/>
       <c r="D523" s="2"/>
       <c r="E523" s="2"/>
       <c r="F523" s="2"/>
       <c r="G523" s="2"/>
     </row>
-    <row r="524">
+    <row r="524" ht="15.75" customHeight="1">
       <c r="A524" s="25" t="s">
         <v>127</v>
       </c>
@@ -11828,7 +11820,7 @@
       <c r="F524" s="2"/>
       <c r="G524" s="2"/>
     </row>
-    <row r="525">
+    <row r="525" ht="15.75" customHeight="1">
       <c r="A525" s="20"/>
       <c r="B525" s="2" t="s">
         <v>10</v>
@@ -11841,7 +11833,7 @@
       <c r="F525" s="2"/>
       <c r="G525" s="2"/>
     </row>
-    <row r="526">
+    <row r="526" ht="15.75" customHeight="1">
       <c r="A526" s="20"/>
       <c r="B526" s="2" t="s">
         <v>12</v>
@@ -11854,12 +11846,12 @@
       <c r="F526" s="2"/>
       <c r="G526" s="2"/>
     </row>
-    <row r="527">
+    <row r="527" ht="15.75" customHeight="1">
       <c r="A527" s="20"/>
       <c r="B527" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C527" s="30">
+      <c r="C527" s="29">
         <v>1.0</v>
       </c>
       <c r="D527" s="2"/>
@@ -11867,18 +11859,18 @@
       <c r="F527" s="2"/>
       <c r="G527" s="2"/>
     </row>
-    <row r="528">
+    <row r="528" ht="15.75" customHeight="1">
       <c r="A528" s="20"/>
       <c r="B528" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C528" s="30"/>
+      <c r="C528" s="29"/>
       <c r="D528" s="2"/>
       <c r="E528" s="2"/>
       <c r="F528" s="2"/>
       <c r="G528" s="2"/>
     </row>
-    <row r="529">
+    <row r="529" ht="15.75" customHeight="1">
       <c r="A529" s="20"/>
       <c r="B529" s="2" t="s">
         <v>20</v>
@@ -11891,7 +11883,7 @@
       <c r="F529" s="2"/>
       <c r="G529" s="2"/>
     </row>
-    <row r="530">
+    <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="20"/>
       <c r="B530" s="7" t="s">
         <v>117</v>
@@ -11904,7 +11896,7 @@
       <c r="F530" s="2"/>
       <c r="G530" s="2"/>
     </row>
-    <row r="531">
+    <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="20"/>
       <c r="B531" s="10" t="s">
         <v>119</v>
@@ -11917,16 +11909,16 @@
       <c r="F531" s="2"/>
       <c r="G531" s="2"/>
     </row>
-    <row r="532">
+    <row r="532" ht="15.75" customHeight="1">
       <c r="A532" s="20"/>
       <c r="B532" s="2"/>
-      <c r="C532" s="30"/>
+      <c r="C532" s="29"/>
       <c r="D532" s="2"/>
       <c r="E532" s="2"/>
       <c r="F532" s="2"/>
       <c r="G532" s="2"/>
     </row>
-    <row r="533">
+    <row r="533" ht="15.75" customHeight="1">
       <c r="A533" s="25" t="s">
         <v>129</v>
       </c>
@@ -11937,7 +11929,7 @@
       <c r="F533" s="2"/>
       <c r="G533" s="2"/>
     </row>
-    <row r="534">
+    <row r="534" ht="15.75" customHeight="1">
       <c r="A534" s="20"/>
       <c r="B534" s="2" t="s">
         <v>10</v>
@@ -11950,7 +11942,7 @@
       <c r="F534" s="2"/>
       <c r="G534" s="2"/>
     </row>
-    <row r="535">
+    <row r="535" ht="15.75" customHeight="1">
       <c r="A535" s="20"/>
       <c r="B535" s="2" t="s">
         <v>12</v>
@@ -11963,12 +11955,12 @@
       <c r="F535" s="2"/>
       <c r="G535" s="2"/>
     </row>
-    <row r="536">
+    <row r="536" ht="15.75" customHeight="1">
       <c r="A536" s="20"/>
       <c r="B536" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C536" s="30">
+      <c r="C536" s="29">
         <v>1.0</v>
       </c>
       <c r="D536" s="2"/>
@@ -11976,18 +11968,18 @@
       <c r="F536" s="2"/>
       <c r="G536" s="2"/>
     </row>
-    <row r="537">
+    <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="20"/>
       <c r="B537" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C537" s="30"/>
+      <c r="C537" s="29"/>
       <c r="D537" s="2"/>
       <c r="E537" s="2"/>
       <c r="F537" s="2"/>
       <c r="G537" s="2"/>
     </row>
-    <row r="538">
+    <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="20"/>
       <c r="B538" s="2" t="s">
         <v>20</v>
@@ -12000,7 +11992,7 @@
       <c r="F538" s="2"/>
       <c r="G538" s="2"/>
     </row>
-    <row r="539">
+    <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="20"/>
       <c r="B539" s="7" t="s">
         <v>117</v>
@@ -12013,7 +12005,7 @@
       <c r="F539" s="2"/>
       <c r="G539" s="2"/>
     </row>
-    <row r="540">
+    <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="20"/>
       <c r="B540" s="10" t="s">
         <v>119</v>
@@ -12026,23 +12018,23 @@
       <c r="F540" s="2"/>
       <c r="G540" s="2"/>
     </row>
-    <row r="541">
+    <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="20"/>
       <c r="B541" s="2"/>
-      <c r="C541" s="30"/>
+      <c r="C541" s="29"/>
       <c r="D541" s="2"/>
       <c r="E541" s="2"/>
       <c r="F541" s="2"/>
       <c r="G541" s="2"/>
     </row>
-    <row r="542">
+    <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="25" t="s">
         <v>131</v>
       </c>
       <c r="B542" s="2"/>
       <c r="C542" s="26"/>
     </row>
-    <row r="543">
+    <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="20"/>
       <c r="B543" s="2" t="s">
         <v>10</v>
@@ -12051,7 +12043,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="544">
+    <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="20"/>
       <c r="B544" s="2" t="s">
         <v>12</v>
@@ -12060,23 +12052,23 @@
         <v>13</v>
       </c>
     </row>
-    <row r="545">
+    <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="20"/>
       <c r="B545" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C545" s="30">
+      <c r="C545" s="29">
         <v>1.0</v>
       </c>
     </row>
-    <row r="546">
+    <row r="546" ht="15.75" customHeight="1">
       <c r="A546" s="20"/>
       <c r="B546" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C546" s="30"/>
-    </row>
-    <row r="547">
+      <c r="C546" s="29"/>
+    </row>
+    <row r="547" ht="15.75" customHeight="1">
       <c r="A547" s="20"/>
       <c r="B547" s="2" t="s">
         <v>20</v>
@@ -12085,7 +12077,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="548">
+    <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="20"/>
       <c r="B548" s="7" t="s">
         <v>117</v>
@@ -12094,7 +12086,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="549">
+    <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="20"/>
       <c r="B549" s="10" t="s">
         <v>119</v>
@@ -12103,12 +12095,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="550">
+    <row r="550" ht="15.75" customHeight="1">
       <c r="A550" s="20"/>
       <c r="B550" s="2"/>
       <c r="C550" s="26"/>
     </row>
-    <row r="551">
+    <row r="551" ht="15.75" customHeight="1">
       <c r="A551" s="25" t="s">
         <v>133</v>
       </c>
@@ -12119,7 +12111,7 @@
       <c r="F551" s="2"/>
       <c r="G551" s="2"/>
     </row>
-    <row r="552">
+    <row r="552" ht="15.75" customHeight="1">
       <c r="A552" s="20"/>
       <c r="B552" s="2" t="s">
         <v>10</v>
@@ -12132,7 +12124,7 @@
       <c r="F552" s="2"/>
       <c r="G552" s="2"/>
     </row>
-    <row r="553">
+    <row r="553" ht="15.75" customHeight="1">
       <c r="A553" s="20"/>
       <c r="B553" s="2" t="s">
         <v>12</v>
@@ -12145,12 +12137,12 @@
       <c r="F553" s="2"/>
       <c r="G553" s="2"/>
     </row>
-    <row r="554">
+    <row r="554" ht="15.75" customHeight="1">
       <c r="A554" s="20"/>
       <c r="B554" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C554" s="30">
+      <c r="C554" s="29">
         <v>1.0</v>
       </c>
       <c r="D554" s="2"/>
@@ -12158,18 +12150,18 @@
       <c r="F554" s="2"/>
       <c r="G554" s="2"/>
     </row>
-    <row r="555">
+    <row r="555" ht="15.75" customHeight="1">
       <c r="A555" s="20"/>
       <c r="B555" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C555" s="30"/>
+      <c r="C555" s="29"/>
       <c r="D555" s="2"/>
       <c r="E555" s="2"/>
       <c r="F555" s="2"/>
       <c r="G555" s="2"/>
     </row>
-    <row r="556">
+    <row r="556" ht="15.75" customHeight="1">
       <c r="A556" s="20"/>
       <c r="B556" s="2" t="s">
         <v>20</v>
@@ -12182,7 +12174,7 @@
       <c r="F556" s="2"/>
       <c r="G556" s="2"/>
     </row>
-    <row r="557">
+    <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="20"/>
       <c r="B557" s="7" t="s">
         <v>117</v>
@@ -12195,7 +12187,7 @@
       <c r="F557" s="2"/>
       <c r="G557" s="2"/>
     </row>
-    <row r="558">
+    <row r="558" ht="15.75" customHeight="1">
       <c r="A558" s="20"/>
       <c r="B558" s="10" t="s">
         <v>119</v>
@@ -12208,19 +12200,19 @@
       <c r="F558" s="2"/>
       <c r="G558" s="2"/>
     </row>
-    <row r="559">
+    <row r="559" ht="15.75" customHeight="1">
       <c r="A559" s="20"/>
       <c r="B559" s="2"/>
       <c r="C559" s="2"/>
     </row>
-    <row r="560">
+    <row r="560" ht="15.75" customHeight="1">
       <c r="A560" s="25" t="s">
         <v>135</v>
       </c>
       <c r="B560" s="2"/>
       <c r="C560" s="26"/>
     </row>
-    <row r="561">
+    <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="20"/>
       <c r="B561" s="2" t="s">
         <v>10</v>
@@ -12229,7 +12221,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="562">
+    <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="20"/>
       <c r="B562" s="2" t="s">
         <v>12</v>
@@ -12238,23 +12230,23 @@
         <v>13</v>
       </c>
     </row>
-    <row r="563">
+    <row r="563" ht="15.75" customHeight="1">
       <c r="A563" s="20"/>
       <c r="B563" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C563" s="30">
+      <c r="C563" s="29">
         <v>1.0</v>
       </c>
     </row>
-    <row r="564">
+    <row r="564" ht="15.75" customHeight="1">
       <c r="A564" s="20"/>
       <c r="B564" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C564" s="30"/>
-    </row>
-    <row r="565">
+      <c r="C564" s="29"/>
+    </row>
+    <row r="565" ht="15.75" customHeight="1">
       <c r="A565" s="20"/>
       <c r="B565" s="2" t="s">
         <v>20</v>
@@ -12263,7 +12255,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="566">
+    <row r="566" ht="15.75" customHeight="1">
       <c r="A566" s="20"/>
       <c r="B566" s="7" t="s">
         <v>117</v>
@@ -12272,7 +12264,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="567">
+    <row r="567" ht="15.75" customHeight="1">
       <c r="A567" s="20"/>
       <c r="B567" s="10" t="s">
         <v>119</v>
